--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -126,6 +126,72 @@
     <t xml:space="preserve">Sawyer Whitaker</t>
   </si>
   <si>
+    <t xml:space="preserve">Adam Leatherland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterloo Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Rusch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur Kowara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carter Kipp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun Yuki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Valvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nico Valvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhys Jenkyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Shephard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Awrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Mustangs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexander Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Conners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colin Mayhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ewan Ferguson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Hawke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koby Sernick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parker McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Nuernberger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Sillett</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ashton Abols</t>
   </si>
   <si>
@@ -192,18 +258,30 @@
     <t xml:space="preserve">Drew McArthur</t>
   </si>
   <si>
+    <t xml:space="preserve">Hayden Cupolo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jack Cohen</t>
   </si>
   <si>
     <t xml:space="preserve">Jack Tiessen</t>
   </si>
   <si>
+    <t xml:space="preserve">Joel Palmer</t>
+  </si>
+  <si>
     <t xml:space="preserve">RJ Moniz</t>
   </si>
   <si>
+    <t xml:space="preserve">Rowan Gelder</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ryan Facchini</t>
   </si>
   <si>
+    <t xml:space="preserve">Wilson Michel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daniel Meron</t>
   </si>
   <si>
@@ -217,6 +295,15 @@
   </si>
   <si>
     <t xml:space="preserve">Rhys Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidan Armitage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Stonkus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Shannon</t>
   </si>
   <si>
     <t xml:space="preserve">21</t>
@@ -292,8 +379,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K36" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K57" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K57"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -312,8 +399,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K24" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K32" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K32"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -669,31 +756,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>59.1</v>
+        <v>58.8</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="E2" t="n">
-        <v>54.3</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="G2" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>23.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>22.2</v>
-      </c>
       <c r="K2" t="n">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="3">
@@ -704,31 +791,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>64.7</v>
+        <v>66.7</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.2</v>
       </c>
       <c r="E3" t="n">
-        <v>44.7</v>
+        <v>51.5</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>15.2</v>
       </c>
       <c r="G3" t="n">
-        <v>21.4</v>
+        <v>17.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I3" t="n">
-        <v>28.6</v>
+        <v>46.2</v>
       </c>
       <c r="J3" t="n">
-        <v>28.6</v>
+        <v>15.4</v>
       </c>
       <c r="K3" t="n">
-        <v>14.3</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="4">
@@ -739,25 +826,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>22.2</v>
+        <v>28.6</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="I4" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -809,31 +896,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>74.2</v>
+        <v>73.3</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="E6" t="n">
-        <v>64.7</v>
+        <v>59.8</v>
       </c>
       <c r="F6" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>38.5</v>
+        <v>45</v>
       </c>
       <c r="J6" t="n">
-        <v>46.2</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>30.8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -844,31 +931,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>74.2</v>
+        <v>76.5</v>
       </c>
       <c r="D7" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="E7" t="n">
-        <v>51.3</v>
+        <v>54.1</v>
       </c>
       <c r="F7" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="G7" t="n">
-        <v>16.1</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="8">
@@ -879,19 +966,19 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>81.8</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>81.8</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -903,7 +990,7 @@
         <v>33.3</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="9">
@@ -914,31 +1001,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>58.8</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>21.3</v>
       </c>
       <c r="E9" t="n">
-        <v>39.4</v>
+        <v>42.7</v>
       </c>
       <c r="F9" t="n">
-        <v>19.4</v>
+        <v>21.3</v>
       </c>
       <c r="G9" t="n">
-        <v>34.6</v>
+        <v>33.3</v>
       </c>
       <c r="H9" t="n">
-        <v>17.6</v>
+        <v>15.4</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>35.7</v>
       </c>
       <c r="J9" t="n">
-        <v>12.5</v>
+        <v>21.4</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="10">
@@ -949,28 +1036,28 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
         <v>100</v>
@@ -1013,31 +1100,31 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>84.8</v>
+        <v>85.1</v>
       </c>
       <c r="D12" t="n">
         <v>16.7</v>
       </c>
       <c r="E12" t="n">
-        <v>68.1</v>
+        <v>68.4</v>
       </c>
       <c r="F12" t="n">
         <v>16.7</v>
       </c>
       <c r="G12" t="n">
-        <v>28.1</v>
+        <v>22.2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>23.1</v>
+        <v>36.4</v>
       </c>
       <c r="J12" t="n">
-        <v>30.8</v>
+        <v>27.3</v>
       </c>
       <c r="K12" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="13">
@@ -1048,31 +1135,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.4</v>
+        <v>54.9</v>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>35.1</v>
+        <v>32.9</v>
       </c>
       <c r="F13" t="n">
-        <v>13.3</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="J13" t="n">
         <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -1083,13 +1170,13 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1101,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J14" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="15">
@@ -1503,31 +1590,31 @@
         <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>52.4</v>
+        <v>-60</v>
       </c>
       <c r="F26" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="H26" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -1538,31 +1625,25 @@
         <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="D27" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="F27" t="n">
-        <v>22.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
       <c r="G27" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -1573,31 +1654,31 @@
         <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>77.8</v>
+        <v>71.4</v>
       </c>
       <c r="D28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" t="n">
         <v>14.3</v>
       </c>
-      <c r="E28" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G28" t="n">
-        <v>43.8</v>
-      </c>
       <c r="H28" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K28" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1608,31 +1689,31 @@
         <v>38</v>
       </c>
       <c r="C29" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="D29" t="n">
-        <v>8.3</v>
+        <v>100</v>
       </c>
       <c r="E29" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>66.7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>50</v>
-      </c>
-      <c r="J29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>62.5</v>
       </c>
     </row>
     <row r="30">
@@ -1646,28 +1727,28 @@
         <v>57.1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E30" t="n">
-        <v>57.1</v>
+        <v>32.1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H30" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1678,31 +1759,31 @@
         <v>38</v>
       </c>
       <c r="C31" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D31" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>32.5</v>
+        <v>75</v>
       </c>
       <c r="F31" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1713,31 +1794,31 @@
         <v>38</v>
       </c>
       <c r="C32" t="n">
+        <v>60</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>100</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>100</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>55.6</v>
-      </c>
       <c r="J32" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1748,28 +1829,28 @@
         <v>38</v>
       </c>
       <c r="C33" t="n">
-        <v>81.2</v>
+        <v>83.3</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E33" t="n">
-        <v>71.2</v>
+        <v>66.6</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="G33" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I33" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1783,31 +1864,31 @@
         <v>38</v>
       </c>
       <c r="C34" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>73.3</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J34" t="n">
         <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -1818,64 +1899,799 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
+        <v>50</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>100</v>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>100</v>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="n">
+        <v>50</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>50</v>
+      </c>
+      <c r="J37" t="n">
+        <v>50</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D38" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>25</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>33.3</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J38" t="n">
         <v>33.3</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K38" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="n">
+        <v>88.9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>88.9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>80</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>25</v>
+      </c>
+      <c r="I41" t="n">
+        <v>40</v>
+      </c>
+      <c r="J41" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="n">
+        <v>80</v>
+      </c>
+      <c r="D42" t="n">
+        <v>25</v>
+      </c>
+      <c r="E42" t="n">
+        <v>55</v>
+      </c>
+      <c r="F42" t="n">
+        <v>25</v>
+      </c>
+      <c r="G42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>25</v>
+      </c>
+      <c r="E43" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F43" t="n">
+        <v>25</v>
+      </c>
+      <c r="G43" t="n">
+        <v>25</v>
+      </c>
+      <c r="H43" t="n">
         <v>33.3</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36"/>
-      <c r="B36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" t="n">
-        <v>71.6</v>
-      </c>
-      <c r="D36" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E36" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G36" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H36" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="J36" t="n">
-        <v>23</v>
-      </c>
-      <c r="K36" t="n">
-        <v>30.8</v>
+      <c r="I43" t="n">
+        <v>50</v>
+      </c>
+      <c r="J43" t="n">
+        <v>50</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>50</v>
+      </c>
+      <c r="J44" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K45" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D46" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>40</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="F47" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>50</v>
+      </c>
+      <c r="J47" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D48" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>100</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="n">
+        <v>75</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>50</v>
+      </c>
+      <c r="J50" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>25</v>
+      </c>
+      <c r="H51" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>60</v>
+      </c>
+      <c r="J51" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" t="n">
+        <v>70</v>
+      </c>
+      <c r="D52" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>25</v>
+      </c>
+      <c r="K52" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" t="n">
+        <v>100</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" t="n">
+        <v>90</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G55" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>50</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" t="n">
+        <v>100</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57"/>
+      <c r="B57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H57" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>51</v>
+      </c>
+      <c r="J57" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K57" t="n">
+        <v>31.4</v>
       </c>
     </row>
   </sheetData>
@@ -1907,22 +2723,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -1931,13 +2747,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
@@ -2012,34 +2828,34 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>53.3</v>
+        <v>56.7</v>
       </c>
       <c r="D4" t="n">
-        <v>65.5</v>
+        <v>65.1</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9</v>
+        <v>14.1</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>22.7</v>
+        <v>15.6</v>
       </c>
       <c r="K4" t="n">
         <v>6.7</v>
@@ -2047,42 +2863,42 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>65.2</v>
+        <v>60.7</v>
       </c>
       <c r="D5" t="n">
-        <v>67.3</v>
+        <v>65.3</v>
       </c>
       <c r="E5" t="n">
-        <v>9.5</v>
+        <v>12.9</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
       <c r="H5" t="n">
-        <v>40.9</v>
+        <v>42.3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.3</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -2117,624 +2933,898 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="D7" t="n">
-        <v>61.5</v>
+        <v>57.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="K7" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>70.6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8"/>
+        <v>28.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8"/>
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>33.3</v>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="K8" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>47.6</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>55.4</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>45.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9"/>
       <c r="G9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>53.8</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H9"/>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>9.5</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
-        <v>43.8</v>
+        <v>56.3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>11.8</v>
       </c>
       <c r="H10" t="n">
-        <v>75</v>
+        <v>58.3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>22.2</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>65.2</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>61.7</v>
+        <v>66.7</v>
       </c>
       <c r="E11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11"/>
       <c r="G11" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>66.7</v>
       </c>
       <c r="D12" t="n">
-        <v>65.8</v>
+        <v>43.8</v>
       </c>
       <c r="E12" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>47.4</v>
+        <v>75</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="D13" t="n">
-        <v>61.5</v>
+        <v>36.8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>16.7</v>
       </c>
-      <c r="H13" t="n">
-        <v>40</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>7.7</v>
-      </c>
       <c r="K13" t="n">
-        <v>-16.7</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>37.5</v>
+        <v>72.9</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>64.9</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="G14" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15"/>
       <c r="G15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>27.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>66.7</v>
+        <v>84</v>
       </c>
       <c r="D16" t="n">
-        <v>57.1</v>
+        <v>65.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="G16" t="n">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>47.4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="K16" t="n">
-        <v>-16.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H17" t="n">
         <v>40</v>
       </c>
-      <c r="D17" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>20</v>
-      </c>
-      <c r="H17" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>25</v>
+        <v>7.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-20</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="D18" t="n">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>-14.3</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
         <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>28.6</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>-25</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>58.1</v>
+        <v>66.7</v>
       </c>
       <c r="D20" t="n">
-        <v>60.9</v>
+        <v>57.1</v>
       </c>
       <c r="E20" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>16.7</v>
       </c>
       <c r="H20" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="K20" t="n">
-        <v>16.6</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>57.8</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21"/>
+        <v>13.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>41.7</v>
+      </c>
       <c r="G21" t="n">
-        <v>66.7</v>
+        <v>11.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="K21" t="n">
-        <v>-66.7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="D22" t="n">
-        <v>63.4</v>
+        <v>87.5</v>
       </c>
       <c r="E22" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>27.3</v>
+        <v>66.7</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C23" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="n">
         <v>40</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D25" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>50</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29"/>
+      <c r="G29" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-66.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" t="n">
+        <v>40</v>
+      </c>
+      <c r="D31" t="n">
         <v>31.6</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E31" t="n">
         <v>7.1</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F31" t="n">
         <v>100</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G31" t="n">
         <v>40</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>33.3</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K31" t="n">
         <v>-20</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24"/>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-5.9</v>
+    <row r="32">
+      <c r="A32"/>
+      <c r="B32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-8.3</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -72,6 +72,9 @@
     <t xml:space="preserve">Gavin Taylor</t>
   </si>
   <si>
+    <t xml:space="preserve">Hayden Cupolo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jaden Leeder</t>
   </si>
   <si>
@@ -126,6 +129,36 @@
     <t xml:space="preserve">Sawyer Whitaker</t>
   </si>
   <si>
+    <t xml:space="preserve">Brandon McMurray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McMaster Marauders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eli Oughton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson McQuade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Dykyj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayan Alazem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Underwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas Velocci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinten Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Stonehouse</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adam Leatherland</t>
   </si>
   <si>
@@ -141,12 +174,21 @@
     <t xml:space="preserve">Carter Kipp</t>
   </si>
   <si>
+    <t xml:space="preserve">Jai Pawa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jun Yuki</t>
   </si>
   <si>
     <t xml:space="preserve">Luca Valvo</t>
   </si>
   <si>
+    <t xml:space="preserve">Max Greaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Todd</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nico Valvo</t>
   </si>
   <si>
@@ -258,9 +300,6 @@
     <t xml:space="preserve">Drew McArthur</t>
   </si>
   <si>
-    <t xml:space="preserve">Hayden Cupolo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jack Cohen</t>
   </si>
   <si>
@@ -295,6 +334,24 @@
   </si>
   <si>
     <t xml:space="preserve">Rhys Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Van Raay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcello Colucci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neal Bhattacharya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McMillan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seth Cabezas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taio Fotiou</t>
   </si>
   <si>
     <t xml:space="preserve">Aidan Armitage</t>
@@ -379,8 +436,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K57" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K70" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K70"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -399,8 +456,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K32" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K39" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K39"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -700,7 +757,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
@@ -756,31 +813,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>58.8</v>
+        <v>58.3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8</v>
+        <v>8.7</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>49.6</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8</v>
+        <v>8.7</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>15.4</v>
       </c>
       <c r="I2" t="n">
-        <v>61.5</v>
+        <v>58.8</v>
       </c>
       <c r="J2" t="n">
-        <v>23.1</v>
+        <v>17.6</v>
       </c>
       <c r="K2" t="n">
-        <v>61.5</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="3">
@@ -791,31 +848,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="D3" t="n">
-        <v>15.2</v>
+        <v>11.9</v>
       </c>
       <c r="E3" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F3" t="n">
-        <v>15.2</v>
+        <v>11.9</v>
       </c>
       <c r="G3" t="n">
-        <v>17.4</v>
+        <v>13.8</v>
       </c>
       <c r="H3" t="n">
-        <v>11.8</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>15.4</v>
+        <v>11.1</v>
       </c>
       <c r="K3" t="n">
-        <v>23.1</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="4">
@@ -826,25 +883,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8</v>
+        <v>8.3</v>
       </c>
       <c r="E4" t="n">
-        <v>43.3</v>
+        <v>40.1</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8</v>
+        <v>8.3</v>
       </c>
       <c r="G4" t="n">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
       <c r="H4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -896,31 +953,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>73.3</v>
+        <v>72.9</v>
       </c>
       <c r="D6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>59.8</v>
+        <v>58.9</v>
       </c>
       <c r="F6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -931,31 +988,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>76.5</v>
+        <v>77.4</v>
       </c>
       <c r="D7" t="n">
-        <v>22.4</v>
+        <v>25.4</v>
       </c>
       <c r="E7" t="n">
-        <v>54.1</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>22.4</v>
+        <v>25.4</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>23.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>31.6</v>
       </c>
       <c r="K7" t="n">
-        <v>43.8</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="8">
@@ -1001,31 +1058,25 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
-      </c>
-      <c r="D9" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>21.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
       <c r="G9" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>35.7</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1036,31 +1087,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>58.8</v>
+        <v>63.5</v>
       </c>
       <c r="D10" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J10" t="n">
         <v>16.7</v>
       </c>
-      <c r="E10" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>33.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>60</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1071,26 +1122,32 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>74.1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>54.1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>29.2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
+      <c r="I11" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>63.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1100,31 +1157,31 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>85.1</v>
+        <v>85.7</v>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>68.4</v>
+        <v>65.7</v>
       </c>
       <c r="F12" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>22.2</v>
+        <v>42.9</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>36.4</v>
+        <v>50</v>
       </c>
       <c r="J12" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>31.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1135,31 +1192,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>54.9</v>
+        <v>83.3</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="E13" t="n">
-        <v>32.9</v>
+        <v>63.8</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1</v>
+        <v>22.4</v>
       </c>
       <c r="H13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>37.5</v>
+        <v>30.8</v>
       </c>
       <c r="J13" t="n">
-        <v>25</v>
+        <v>34.6</v>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="14">
@@ -1170,31 +1227,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>54.3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>33.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I14" t="n">
-        <v>16.7</v>
+        <v>45.5</v>
       </c>
       <c r="J14" t="n">
-        <v>83.3</v>
+        <v>22.7</v>
       </c>
       <c r="K14" t="n">
-        <v>33.3</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="15">
@@ -1202,69 +1259,69 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
       <c r="C16" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>74.2</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="H16" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1272,34 +1329,34 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="18">
@@ -1307,31 +1364,31 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>8.3</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>47.9</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>8.3</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1342,34 +1399,34 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>90.9</v>
+        <v>56.2</v>
       </c>
       <c r="D19" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
         <v>14.3</v>
       </c>
-      <c r="E19" t="n">
-        <v>76.6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
       <c r="K19" t="n">
-        <v>83.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1377,34 +1434,34 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>76.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K20" t="n">
         <v>83.3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>67.9</v>
-      </c>
-      <c r="F20" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="G20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I20" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1412,34 +1469,34 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>60</v>
+        <v>83.3</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>15.4</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>67.9</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>15.4</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I21" t="n">
-        <v>71.4</v>
+        <v>66.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1447,34 +1504,34 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>16.7</v>
+        <v>71.4</v>
       </c>
       <c r="J22" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="23">
@@ -1482,34 +1539,34 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>14.3</v>
       </c>
       <c r="I23" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
       <c r="J23" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="24">
@@ -1517,34 +1574,34 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>63.6</v>
+        <v>62.5</v>
       </c>
       <c r="D24" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>41.4</v>
+        <v>62.5</v>
       </c>
       <c r="F24" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="I24" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J24" t="n">
+        <v>40</v>
+      </c>
+      <c r="K24" t="n">
         <v>20</v>
-      </c>
-      <c r="K24" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -1552,34 +1609,34 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>80</v>
+      </c>
+      <c r="J25" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" t="n">
         <v>40</v>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="n">
-        <v>30</v>
-      </c>
-      <c r="F25" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>25</v>
-      </c>
-      <c r="J25" t="n">
-        <v>50</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1587,57 +1644,63 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C26" t="n">
         <v>40</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>-60</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
         <v>39</v>
       </c>
-      <c r="B27" t="s">
-        <v>38</v>
-      </c>
       <c r="C27" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I27" t="n">
         <v>100</v>
-      </c>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>50</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1651,34 +1714,34 @@
         <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" t="n">
-        <v>71.4</v>
+        <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>21.4</v>
+        <v>60</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>33.3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1686,31 +1749,31 @@
         <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" t="n">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
-        <v>-16.7</v>
+        <v>67.5</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K29" t="n">
         <v>66.7</v>
@@ -1721,34 +1784,34 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="D30" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>25</v>
       </c>
-      <c r="E30" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="J30" t="n">
         <v>25</v>
       </c>
-      <c r="G30" t="n">
-        <v>40</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>100</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -1756,34 +1819,34 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
-        <v>75</v>
+        <v>17.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="32">
@@ -1791,16 +1854,16 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1809,10 +1872,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1826,34 +1889,34 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33" t="n">
-        <v>83.3</v>
+        <v>71.4</v>
       </c>
       <c r="D33" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="E33" t="n">
-        <v>66.6</v>
+        <v>38.1</v>
       </c>
       <c r="F33" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="G33" t="n">
         <v>42.9</v>
       </c>
       <c r="H33" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>100</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1861,34 +1924,34 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>80</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-51.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>80</v>
+      </c>
+      <c r="G34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
         <v>100</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>100</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>50</v>
-      </c>
       <c r="J34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1896,19 +1959,19 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1917,185 +1980,179 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>8.3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
       </c>
       <c r="C37" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="F37" t="n">
-        <v>11.1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>50</v>
       </c>
       <c r="J37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
         <v>49</v>
       </c>
       <c r="C38" t="n">
-        <v>85.7</v>
+        <v>78.6</v>
       </c>
       <c r="D38" t="n">
-        <v>22.2</v>
+        <v>36.4</v>
       </c>
       <c r="E38" t="n">
-        <v>63.5</v>
+        <v>42.2</v>
       </c>
       <c r="F38" t="n">
-        <v>22.2</v>
+        <v>36.4</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I38" t="n">
         <v>33.3</v>
       </c>
       <c r="J38" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
         <v>49</v>
       </c>
       <c r="C39" t="n">
-        <v>88.9</v>
+        <v>76.9</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E39" t="n">
-        <v>88.9</v>
+        <v>51.9</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H39" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K39" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
         <v>49</v>
       </c>
       <c r="C40" t="n">
-        <v>78.6</v>
+        <v>83.3</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E40" t="n">
-        <v>78.6</v>
+        <v>54.7</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G40" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I40" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2103,247 +2160,247 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
         <v>49</v>
       </c>
       <c r="C41" t="n">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E41" t="n">
-        <v>64.3</v>
+        <v>32.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G41" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>60.7</v>
+        <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H43" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
       </c>
       <c r="C44" t="n">
-        <v>90.9</v>
+        <v>60</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E44" t="n">
-        <v>90.9</v>
+        <v>43.3</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
         <v>50</v>
       </c>
       <c r="J44" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
       </c>
       <c r="C45" t="n">
-        <v>77.8</v>
+        <v>53.8</v>
       </c>
       <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H45" t="n">
         <v>16.7</v>
       </c>
-      <c r="E45" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>11.1</v>
-      </c>
       <c r="I45" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="J45" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="D46" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E46" t="n">
-        <v>66.9</v>
+        <v>66.6</v>
       </c>
       <c r="F46" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="G46" t="n">
-        <v>6.7</v>
+        <v>42.9</v>
       </c>
       <c r="H46" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="I46" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="D47" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="E47" t="n">
-        <v>52.4</v>
+        <v>72.7</v>
       </c>
       <c r="F47" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="G47" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="I47" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J47" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48">
@@ -2351,104 +2408,104 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I48" t="n">
         <v>60</v>
       </c>
-      <c r="C48" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="D48" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E48" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="F48" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G48" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
+        <v>40</v>
+      </c>
+      <c r="K48" t="n">
         <v>100</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C49" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>63.5</v>
+        <v>50</v>
       </c>
       <c r="F49" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" t="s">
         <v>63</v>
       </c>
-      <c r="B50" t="s">
-        <v>60</v>
-      </c>
       <c r="C50" t="n">
-        <v>75</v>
+        <v>61.5</v>
       </c>
       <c r="D50" t="n">
-        <v>8.3</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="n">
-        <v>66.7</v>
+        <v>50.4</v>
       </c>
       <c r="F50" t="n">
-        <v>8.3</v>
+        <v>11.1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I50" t="n">
         <v>50</v>
       </c>
       <c r="J50" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="K50" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2456,34 +2513,34 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C51" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E51" t="n">
-        <v>57.1</v>
+        <v>63.5</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G51" t="n">
         <v>25</v>
       </c>
       <c r="H51" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K51" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
@@ -2491,34 +2548,34 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C52" t="n">
-        <v>70</v>
+        <v>88.9</v>
       </c>
       <c r="D52" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>32.5</v>
+        <v>88.9</v>
       </c>
       <c r="F52" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I52" t="n">
-        <v>37.5</v>
+        <v>80</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -2526,34 +2583,34 @@
         <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C53" t="n">
-        <v>100</v>
+        <v>78.6</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>78.6</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>55.6</v>
+        <v>85.7</v>
       </c>
       <c r="J53" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2561,34 +2618,34 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>25</v>
+      </c>
+      <c r="I54" t="n">
+        <v>40</v>
+      </c>
+      <c r="J54" t="n">
+        <v>20</v>
+      </c>
+      <c r="K54" t="n">
         <v>60</v>
-      </c>
-      <c r="C54" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="F54" t="n">
-        <v>10</v>
-      </c>
-      <c r="G54" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2596,34 +2653,34 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C55" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D55" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E55" t="n">
-        <v>73.3</v>
+        <v>55</v>
       </c>
       <c r="F55" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G55" t="n">
-        <v>18.2</v>
+        <v>11.1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="56">
@@ -2631,67 +2688,522 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>25</v>
+      </c>
+      <c r="E56" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>25</v>
+      </c>
+      <c r="G56" t="n">
+        <v>25</v>
+      </c>
+      <c r="H56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>50</v>
+      </c>
+      <c r="J56" t="n">
+        <v>50</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>50</v>
+      </c>
+      <c r="J57" t="n">
+        <v>25</v>
+      </c>
+      <c r="K57" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K58" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I59" t="n">
+        <v>40</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="H60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>50</v>
+      </c>
+      <c r="J60" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" t="n">
+        <v>75</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>50</v>
+      </c>
+      <c r="J63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>25</v>
+      </c>
+      <c r="H64" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I64" t="n">
         <v>60</v>
       </c>
-      <c r="C56" t="n">
+      <c r="J64" t="n">
+        <v>20</v>
+      </c>
+      <c r="K64" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" t="n">
+        <v>70</v>
+      </c>
+      <c r="D65" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J65" t="n">
+        <v>25</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" t="n">
         <v>100</v>
       </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
         <v>100</v>
       </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="F67" t="n">
+        <v>10</v>
+      </c>
+      <c r="G67" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="n">
+        <v>90</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E68" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G68" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>33.3</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J68" t="n">
+        <v>50</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" t="n">
+        <v>100</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>100</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>33.3</v>
       </c>
-      <c r="K56" t="n">
+      <c r="J69" t="n">
         <v>33.3</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57"/>
-      <c r="B57" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="K69" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70"/>
+      <c r="B70" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" t="n">
+        <v>71.1</v>
+      </c>
+      <c r="D70" t="n">
         <v>15.5</v>
       </c>
-      <c r="E57" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F57" t="n">
+      <c r="E70" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F70" t="n">
         <v>15.5</v>
       </c>
-      <c r="G57" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H57" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>51</v>
-      </c>
-      <c r="J57" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K57" t="n">
-        <v>31.4</v>
+      <c r="G70" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>
@@ -2708,7 +3220,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="5.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
@@ -2723,22 +3235,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -2747,13 +3259,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2">
@@ -2764,31 +3276,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>71.4</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>65.4</v>
+        <v>66.7</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="K2" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2828,112 +3340,112 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>56.7</v>
+        <v>53.9</v>
       </c>
       <c r="D4" t="n">
-        <v>65.1</v>
+        <v>65.4</v>
       </c>
       <c r="E4" t="n">
-        <v>14.1</v>
+        <v>16.5</v>
       </c>
       <c r="F4" t="n">
         <v>33.3</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>54.3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>15.6</v>
+        <v>19.3</v>
       </c>
       <c r="K4" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>60.7</v>
+        <v>59.4</v>
       </c>
       <c r="D5" t="n">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="E5" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>42.3</v>
+        <v>43.3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.1</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>61.5</v>
+        <v>54.5</v>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>60.8</v>
       </c>
       <c r="E6" t="n">
-        <v>23.1</v>
+        <v>20.6</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>8.7</v>
       </c>
       <c r="H6" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>27.3</v>
+        <v>23.5</v>
       </c>
       <c r="K6" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -2968,7 +3480,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -3003,38 +3515,42 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="D9" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H9" t="n">
         <v>40</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9"/>
-      <c r="G9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9"/>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="K9" t="n">
-        <v>-100</v>
+        <v>-26.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -3069,7 +3585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -3102,42 +3618,42 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="D12" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>8.8</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>35.7</v>
       </c>
       <c r="H12" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="K12" t="n">
-        <v>-12.5</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -3170,7 +3686,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -3205,7 +3721,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -3238,10 +3754,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
         <v>84</v>
@@ -3273,10 +3789,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
         <v>50</v>
@@ -3308,10 +3824,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
         <v>37.5</v>
@@ -3343,10 +3859,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
         <v>50</v>
@@ -3378,10 +3894,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="n">
         <v>66.7</v>
@@ -3413,63 +3929,61 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>63</v>
+        <v>33.3</v>
       </c>
       <c r="D21" t="n">
-        <v>57.8</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="F22"/>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3483,130 +3997,126 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C23" t="n">
-        <v>61.5</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>63.2</v>
+        <v>22.2</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23" t="n">
-        <v>30.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23"/>
       <c r="G23" t="n">
-        <v>15.4</v>
+        <v>50</v>
       </c>
       <c r="H23" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C24" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="D24" t="n">
-        <v>65.3</v>
+        <v>64.3</v>
       </c>
       <c r="E24" t="n">
-        <v>31.4</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>12.5</v>
+        <v>46.2</v>
       </c>
       <c r="K24" t="n">
-        <v>8.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D25" t="n">
-        <v>41.2</v>
+        <v>66.7</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-20</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C26" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>44.1</v>
+        <v>80</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
-        <v>33.3</v>
-      </c>
+      <c r="F26"/>
       <c r="G26" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>50</v>
@@ -3615,216 +4125,461 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G27" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>28.6</v>
+        <v>23.5</v>
       </c>
       <c r="K27" t="n">
-        <v>-25</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="n">
         <v>100</v>
       </c>
-      <c r="B28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" t="n">
-        <v>58.1</v>
-      </c>
       <c r="D28" t="n">
-        <v>60.9</v>
+        <v>87.5</v>
       </c>
       <c r="E28" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>74.7</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29"/>
+        <v>28.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>50</v>
+      </c>
       <c r="G29" t="n">
-        <v>66.7</v>
+        <v>3.8</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="K29" t="n">
-        <v>-66.7</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>77.8</v>
+        <v>61.5</v>
       </c>
       <c r="D30" t="n">
-        <v>63.4</v>
+        <v>63.2</v>
       </c>
       <c r="E30" t="n">
-        <v>17.6</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>30.8</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H30" t="n">
-        <v>27.3</v>
+        <v>66.7</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>27.3</v>
+        <v>21.4</v>
       </c>
       <c r="K30" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C31" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="n">
         <v>40</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D32" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>50</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="n">
+        <v>50</v>
+      </c>
+      <c r="D34" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>25</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E35" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-66.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>50</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K37" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="n">
+        <v>40</v>
+      </c>
+      <c r="D38" t="n">
         <v>31.6</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E38" t="n">
         <v>7.1</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F38" t="n">
         <v>100</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G38" t="n">
         <v>40</v>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>33.3</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K38" t="n">
         <v>-20</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32"/>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F32" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="G32" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H32" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="I32" t="n">
+    <row r="39">
+      <c r="A39"/>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.1</v>
       </c>
-      <c r="J32" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-8.3</v>
+      <c r="J39" t="n">
+        <v>16</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-5.2</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -99,6 +99,9 @@
     <t xml:space="preserve">Guelph Gryphons</t>
   </si>
   <si>
+    <t xml:space="preserve">Andrew Johnston</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brendan Cooper</t>
   </si>
   <si>
@@ -123,16 +126,31 @@
     <t xml:space="preserve">Noah Chang</t>
   </si>
   <si>
+    <t xml:space="preserve">Nolan Boyle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nolan Scicluna</t>
   </si>
   <si>
     <t xml:space="preserve">Sawyer Whitaker</t>
   </si>
   <si>
+    <t xml:space="preserve">Thomas Cullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anden Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McMaster Marauders</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brandon McMurray</t>
   </si>
   <si>
-    <t xml:space="preserve">McMaster Marauders</t>
+    <t xml:space="preserve">Declan Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Cheng</t>
   </si>
   <si>
     <t xml:space="preserve">Eli Oughton</t>
@@ -141,12 +159,21 @@
     <t xml:space="preserve">Jackson McQuade</t>
   </si>
   <si>
+    <t xml:space="preserve">Jeremy Kim</t>
+  </si>
+  <si>
     <t xml:space="preserve">John Dykyj</t>
   </si>
   <si>
+    <t xml:space="preserve">Justin White</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kayan Alazem</t>
   </si>
   <si>
+    <t xml:space="preserve">Lucas Grant</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matt Underwood</t>
   </si>
   <si>
@@ -321,22 +348,37 @@
     <t xml:space="preserve">Wilson Michel</t>
   </si>
   <si>
+    <t xml:space="preserve">Alexandre Picard</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daniel Meron</t>
   </si>
   <si>
     <t xml:space="preserve">Harrison Young</t>
   </si>
   <si>
+    <t xml:space="preserve">J.C. Reynolds</t>
+  </si>
+  <si>
     <t xml:space="preserve">Landon Hutar</t>
   </si>
   <si>
     <t xml:space="preserve">Logan Miziolek</t>
   </si>
   <si>
+    <t xml:space="preserve">Max Rutherford</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rhys Montgomery</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Van Raay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erik Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaden Fonseca</t>
   </si>
   <si>
     <t xml:space="preserve">Marcello Colucci</t>
@@ -436,8 +478,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K70" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K79" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K79"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -456,8 +498,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K39" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K44" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K44"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -813,31 +855,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>58.3</v>
+        <v>60.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7</v>
+        <v>5.2</v>
       </c>
       <c r="E2" t="n">
-        <v>49.6</v>
+        <v>55.3</v>
       </c>
       <c r="F2" t="n">
-        <v>8.7</v>
+        <v>5.2</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>18.9</v>
       </c>
       <c r="H2" t="n">
-        <v>15.4</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>17.6</v>
+        <v>28.6</v>
       </c>
       <c r="K2" t="n">
-        <v>52.9</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="3">
@@ -848,31 +890,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>63.2</v>
+        <v>76.1</v>
       </c>
       <c r="D3" t="n">
-        <v>11.9</v>
+        <v>10.2</v>
       </c>
       <c r="E3" t="n">
-        <v>51.3</v>
+        <v>65.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11.9</v>
+        <v>10.2</v>
       </c>
       <c r="G3" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>38.9</v>
       </c>
       <c r="J3" t="n">
-        <v>11.1</v>
+        <v>30.6</v>
       </c>
       <c r="K3" t="n">
-        <v>27.8</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="4">
@@ -883,22 +925,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>8.3</v>
+        <v>10.7</v>
       </c>
       <c r="E4" t="n">
-        <v>40.1</v>
+        <v>39.3</v>
       </c>
       <c r="F4" t="n">
-        <v>8.3</v>
+        <v>10.7</v>
       </c>
       <c r="G4" t="n">
-        <v>29.4</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="I4" t="n">
         <v>57.1</v>
@@ -953,31 +995,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>72.9</v>
+        <v>71.9</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>10.1</v>
       </c>
       <c r="E6" t="n">
-        <v>58.9</v>
+        <v>61.8</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>10.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="I6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="7">
@@ -988,31 +1030,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>77.4</v>
+        <v>81.5</v>
       </c>
       <c r="D7" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>55.9</v>
       </c>
       <c r="F7" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="G7" t="n">
-        <v>23.8</v>
+        <v>25.5</v>
       </c>
       <c r="H7" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="I7" t="n">
-        <v>42.1</v>
+        <v>48.5</v>
       </c>
       <c r="J7" t="n">
-        <v>31.6</v>
+        <v>24.2</v>
       </c>
       <c r="K7" t="n">
-        <v>42.1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="8">
@@ -1023,31 +1065,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>81.6</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>81.6</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="K8" t="n">
-        <v>83.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="9">
@@ -1087,31 +1129,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>63.5</v>
+        <v>67.4</v>
       </c>
       <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>23.3</v>
       </c>
-      <c r="E10" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>37</v>
-      </c>
-      <c r="H10" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16.7</v>
-      </c>
       <c r="K10" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -1122,31 +1164,31 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>74.1</v>
+        <v>76.5</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="E11" t="n">
-        <v>54.1</v>
+        <v>62.2</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="G11" t="n">
-        <v>29.2</v>
+        <v>34.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I11" t="n">
-        <v>36.4</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="K11" t="n">
-        <v>63.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="12">
@@ -1157,31 +1199,31 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="n">
-        <v>65.7</v>
+        <v>63.3</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G12" t="n">
-        <v>42.9</v>
+        <v>30.8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="13">
@@ -1192,31 +1234,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>83.3</v>
+        <v>80.8</v>
       </c>
       <c r="D13" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="E13" t="n">
-        <v>63.8</v>
+        <v>64.3</v>
       </c>
       <c r="F13" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="G13" t="n">
-        <v>22.4</v>
+        <v>26.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>30.8</v>
+        <v>39.5</v>
       </c>
       <c r="J13" t="n">
-        <v>34.6</v>
+        <v>31.6</v>
       </c>
       <c r="K13" t="n">
-        <v>30.8</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="14">
@@ -1227,31 +1269,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>54.3</v>
+        <v>55.4</v>
       </c>
       <c r="D14" t="n">
-        <v>21.1</v>
+        <v>14.9</v>
       </c>
       <c r="E14" t="n">
-        <v>33.2</v>
+        <v>40.5</v>
       </c>
       <c r="F14" t="n">
-        <v>21.1</v>
+        <v>14.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>11.8</v>
       </c>
       <c r="H14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I14" t="n">
-        <v>45.5</v>
+        <v>51.5</v>
       </c>
       <c r="J14" t="n">
-        <v>22.7</v>
+        <v>21.2</v>
       </c>
       <c r="K14" t="n">
-        <v>31.8</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="15">
@@ -1332,31 +1374,31 @@
         <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="D17" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="n">
-        <v>74.2</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="G17" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>14.3</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>16.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -1367,31 +1409,31 @@
         <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>86.7</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>77.6</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="19">
@@ -1402,28 +1444,28 @@
         <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>8.3</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>47.9</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>8.3</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1437,31 +1479,31 @@
         <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>90.9</v>
+        <v>62.5</v>
       </c>
       <c r="D20" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>76.6</v>
+        <v>52.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>8.3</v>
+        <v>20.8</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I20" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="J20" t="n">
-        <v>16.7</v>
+        <v>54.5</v>
       </c>
       <c r="K20" t="n">
-        <v>83.3</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="21">
@@ -1472,31 +1514,31 @@
         <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>83.3</v>
+        <v>82.1</v>
       </c>
       <c r="D21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="J21" t="n">
         <v>15.4</v>
       </c>
-      <c r="E21" t="n">
-        <v>67.9</v>
-      </c>
-      <c r="F21" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H21" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="22">
@@ -1507,31 +1549,31 @@
         <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>31.8</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I22" t="n">
-        <v>71.4</v>
+        <v>33.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K22" t="n">
-        <v>42.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="23">
@@ -1542,31 +1584,31 @@
         <v>27</v>
       </c>
       <c r="C23" t="n">
-        <v>80</v>
+        <v>71.9</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>67.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H23" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I23" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="J23" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -1577,31 +1619,31 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>62.5</v>
+        <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="E24" t="n">
-        <v>62.5</v>
+        <v>78.4</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="H24" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="I24" t="n">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="J24" t="n">
         <v>40</v>
       </c>
       <c r="K24" t="n">
-        <v>20</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="25">
@@ -1612,31 +1654,31 @@
         <v>27</v>
       </c>
       <c r="C25" t="n">
-        <v>63.6</v>
+        <v>59.3</v>
       </c>
       <c r="D25" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="E25" t="n">
-        <v>41.4</v>
+        <v>50.2</v>
       </c>
       <c r="F25" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="G25" t="n">
-        <v>11.1</v>
+        <v>42.1</v>
       </c>
       <c r="H25" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="I25" t="n">
-        <v>80</v>
+        <v>33.3</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K25" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="26">
@@ -1647,28 +1689,28 @@
         <v>27</v>
       </c>
       <c r="C26" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="J26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1679,139 +1721,139 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="H27" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>60</v>
+        <v>48.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>40.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="K28" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>87.5</v>
+        <v>56.2</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>67.5</v>
+        <v>26.2</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>37.5</v>
+        <v>41.7</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="J29" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
         <v>42</v>
       </c>
-      <c r="B30" t="s">
-        <v>39</v>
-      </c>
       <c r="C30" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D30" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="F30" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K30" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1819,31 +1861,31 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C31" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>17.5</v>
+        <v>60</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K31" t="n">
         <v>66.7</v>
@@ -1854,28 +1896,28 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C32" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="n">
-        <v>33.3</v>
+        <v>27.5</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1889,34 +1931,34 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C33" t="n">
-        <v>71.4</v>
+        <v>47.1</v>
       </c>
       <c r="D33" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="E33" t="n">
-        <v>38.1</v>
+        <v>30.4</v>
       </c>
       <c r="F33" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="G33" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="34">
@@ -1924,22 +1966,22 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C34" t="n">
-        <v>28.6</v>
+        <v>66.7</v>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
-        <v>-51.4</v>
+        <v>41.7</v>
       </c>
       <c r="F34" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1951,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -1959,34 +2001,34 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>87.5</v>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>67.5</v>
       </c>
       <c r="F35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K35" t="n">
         <v>66.7</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1994,343 +2036,341 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C36" t="n">
-        <v>53.8</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="G36" t="n">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G36"/>
       <c r="H36" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I36" t="n">
-        <v>50</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>100</v>
-      </c>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
+        <v>57.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E37" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>17.6</v>
+      </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C38" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="D38" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>42.2</v>
+        <v>50</v>
       </c>
       <c r="F38" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>76.9</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G39" t="n">
         <v>25</v>
       </c>
-      <c r="E39" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="F39" t="n">
-        <v>25</v>
-      </c>
-      <c r="G39" t="n">
-        <v>9.1</v>
-      </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J39" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C40" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="D40" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>54.7</v>
+        <v>66.7</v>
       </c>
       <c r="F40" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H40" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C41" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="D41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>50</v>
+      </c>
+      <c r="J41" t="n">
         <v>25</v>
       </c>
-      <c r="E41" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>25</v>
-      </c>
-      <c r="G41" t="n">
-        <v>40</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>100</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C42" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E42" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>100</v>
+        <v>36.4</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>100</v>
+        <v>-33.6</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G43" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>66.7</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>100</v>
-      </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="D44" t="n">
-        <v>16.7</v>
+        <v>38.5</v>
       </c>
       <c r="E44" t="n">
-        <v>43.3</v>
+        <v>24</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>38.5</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="J44" t="n">
         <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
         <v>58</v>
-      </c>
-      <c r="B45" t="s">
-        <v>49</v>
       </c>
       <c r="C45" t="n">
         <v>53.8</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="E45" t="n">
-        <v>53.8</v>
+        <v>8.3</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="G45" t="n">
+        <v>25</v>
+      </c>
+      <c r="H45" t="n">
         <v>14.3</v>
       </c>
-      <c r="H45" t="n">
-        <v>16.7</v>
-      </c>
       <c r="I45" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -2338,34 +2378,28 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C46" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="D46" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E46" t="n">
-        <v>66.6</v>
-      </c>
-      <c r="F46" t="n">
-        <v>16.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
       <c r="G46" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
@@ -2373,34 +2407,34 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C47" t="n">
-        <v>81.8</v>
+        <v>78.6</v>
       </c>
       <c r="D47" t="n">
-        <v>9.1</v>
+        <v>36.4</v>
       </c>
       <c r="E47" t="n">
-        <v>72.7</v>
+        <v>42.2</v>
       </c>
       <c r="F47" t="n">
-        <v>9.1</v>
+        <v>36.4</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="H47" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="I47" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="J47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2408,66 +2442,66 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C48" t="n">
-        <v>66.7</v>
+        <v>76.9</v>
       </c>
       <c r="D48" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>58.4</v>
+        <v>51.9</v>
       </c>
       <c r="F48" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="G48" t="n">
         <v>9.1</v>
       </c>
       <c r="H48" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="J48" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>54.7</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2475,34 +2509,34 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C50" t="n">
-        <v>61.5</v>
+        <v>57.1</v>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="E50" t="n">
-        <v>50.4</v>
+        <v>32.1</v>
       </c>
       <c r="F50" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H50" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2513,34 +2547,34 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C51" t="n">
-        <v>85.7</v>
+        <v>75</v>
       </c>
       <c r="D51" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>63.5</v>
+        <v>75</v>
       </c>
       <c r="F51" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2548,34 +2582,34 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C52" t="n">
-        <v>88.9</v>
+        <v>100</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>88.9</v>
+        <v>100</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H52" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
@@ -2583,34 +2617,34 @@
         <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C53" t="n">
-        <v>78.6</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E53" t="n">
-        <v>78.6</v>
+        <v>43.3</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G53" t="n">
-        <v>9.1</v>
+        <v>20</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I53" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -2618,25 +2652,25 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C54" t="n">
-        <v>64.3</v>
+        <v>53.8</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>64.3</v>
+        <v>53.8</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="H54" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="I54" t="n">
         <v>40</v>
@@ -2645,7 +2679,7 @@
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
@@ -2653,34 +2687,34 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="D55" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="E55" t="n">
-        <v>55</v>
+        <v>66.6</v>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G55" t="n">
-        <v>11.1</v>
+        <v>42.9</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I55" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2688,34 +2722,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C56" t="n">
-        <v>85.7</v>
+        <v>81.8</v>
       </c>
       <c r="D56" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>20</v>
+      </c>
+      <c r="I56" t="n">
+        <v>75</v>
+      </c>
+      <c r="J56" t="n">
         <v>25</v>
       </c>
-      <c r="E56" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="F56" t="n">
-        <v>25</v>
-      </c>
-      <c r="G56" t="n">
-        <v>25</v>
-      </c>
-      <c r="H56" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I56" t="n">
-        <v>50</v>
-      </c>
-      <c r="J56" t="n">
-        <v>50</v>
-      </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57">
@@ -2723,104 +2757,104 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C57" t="n">
-        <v>90.9</v>
+        <v>66.7</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E57" t="n">
-        <v>90.9</v>
+        <v>58.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I57" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K57" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C58" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="D58" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" t="s">
         <v>72</v>
       </c>
-      <c r="B59" t="s">
-        <v>63</v>
-      </c>
       <c r="C59" t="n">
-        <v>85.7</v>
+        <v>61.5</v>
       </c>
       <c r="D59" t="n">
-        <v>18.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="n">
-        <v>66.9</v>
+        <v>50.4</v>
       </c>
       <c r="F59" t="n">
-        <v>18.8</v>
+        <v>11.1</v>
       </c>
       <c r="G59" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="I59" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K59" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2828,343 +2862,343 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C60" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="D60" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="E60" t="n">
-        <v>52.4</v>
+        <v>63.5</v>
       </c>
       <c r="F60" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="G60" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
       <c r="H60" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J60" t="n">
         <v>33.3</v>
       </c>
       <c r="K60" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C61" t="n">
-        <v>55.6</v>
+        <v>88.9</v>
       </c>
       <c r="D61" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>33.4</v>
+        <v>88.9</v>
       </c>
       <c r="F61" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I61" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C62" t="n">
-        <v>77.8</v>
+        <v>78.6</v>
       </c>
       <c r="D62" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>63.5</v>
+        <v>78.6</v>
       </c>
       <c r="F62" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>43.8</v>
+        <v>9.1</v>
       </c>
       <c r="H62" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C63" t="n">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="D63" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>66.7</v>
+        <v>64.3</v>
       </c>
       <c r="F63" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I63" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J63" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C64" t="n">
+        <v>80</v>
+      </c>
+      <c r="D64" t="n">
+        <v>25</v>
+      </c>
+      <c r="E64" t="n">
+        <v>55</v>
+      </c>
+      <c r="F64" t="n">
+        <v>25</v>
+      </c>
+      <c r="G64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
         <v>57.1</v>
       </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>25</v>
-      </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>14.3</v>
       </c>
-      <c r="I64" t="n">
-        <v>60</v>
-      </c>
-      <c r="J64" t="n">
-        <v>20</v>
-      </c>
       <c r="K64" t="n">
-        <v>60</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C65" t="n">
-        <v>70</v>
+        <v>85.7</v>
       </c>
       <c r="D65" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="E65" t="n">
-        <v>32.5</v>
+        <v>60.7</v>
       </c>
       <c r="F65" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="G65" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I65" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C66" t="n">
-        <v>100</v>
+        <v>90.9</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>100</v>
+        <v>90.9</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J66" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="K66" t="n">
-        <v>22.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C67" t="n">
-        <v>81.2</v>
+        <v>77.8</v>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E67" t="n">
-        <v>71.2</v>
+        <v>61.1</v>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="G67" t="n">
-        <v>14.3</v>
+        <v>4.2</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I67" t="n">
-        <v>28.6</v>
+        <v>66.7</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C68" t="n">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="D68" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E68" t="n">
-        <v>73.3</v>
+        <v>66.9</v>
       </c>
       <c r="F68" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="G68" t="n">
-        <v>18.2</v>
+        <v>6.7</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I68" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="J68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" t="s">
         <v>83</v>
       </c>
-      <c r="B69" t="s">
-        <v>74</v>
-      </c>
       <c r="C69" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E69" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I69" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J69" t="n">
         <v>33.3</v>
@@ -3174,36 +3208,351 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70"/>
+      <c r="A70" t="s">
+        <v>84</v>
+      </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C70" t="n">
-        <v>71.1</v>
+        <v>55.6</v>
       </c>
       <c r="D70" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="E70" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F70" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>100</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="H71" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I71" t="n">
+        <v>100</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>86</v>
+      </c>
+      <c r="B72" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72" t="n">
+        <v>75</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>50</v>
+      </c>
+      <c r="J72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>25</v>
+      </c>
+      <c r="H73" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>60</v>
+      </c>
+      <c r="J73" t="n">
+        <v>20</v>
+      </c>
+      <c r="K73" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>88</v>
+      </c>
+      <c r="B74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" t="n">
+        <v>70</v>
+      </c>
+      <c r="D74" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>25</v>
+      </c>
+      <c r="K74" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>89</v>
+      </c>
+      <c r="B75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" t="n">
+        <v>100</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>100</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>90</v>
+      </c>
+      <c r="B76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="n">
+        <v>90</v>
+      </c>
+      <c r="D77" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E77" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G77" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>50</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" t="n">
+        <v>100</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>100</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J78" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79"/>
+      <c r="B79" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="D79" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E79" t="n">
         <v>54.8</v>
       </c>
-      <c r="F70" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G70" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H70" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="I70" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="J70" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K70" t="n">
-        <v>32.2</v>
+      <c r="F79" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G79" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="I79" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="J79" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="K79" t="n">
+        <v>31.3</v>
       </c>
     </row>
   </sheetData>
@@ -3235,22 +3584,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -3259,13 +3608,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2">
@@ -3340,7 +3689,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -3375,16 +3724,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>59.4</v>
+        <v>60.6</v>
       </c>
       <c r="D5" t="n">
-        <v>65.5</v>
+        <v>65.9</v>
       </c>
       <c r="E5" t="n">
         <v>15.8</v>
@@ -3393,51 +3742,51 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H5" t="n">
-        <v>43.3</v>
+        <v>45.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.2</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>54.5</v>
+        <v>47.1</v>
       </c>
       <c r="D6" t="n">
-        <v>60.8</v>
+        <v>59.5</v>
       </c>
       <c r="E6" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="F6" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>25</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>23.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -3445,37 +3794,37 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>42.9</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>57.7</v>
+        <v>58.5</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="F7" t="n">
-        <v>28.6</v>
+        <v>27.3</v>
       </c>
       <c r="G7" t="n">
-        <v>14.3</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>55.6</v>
+        <v>38.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8</v>
+        <v>19.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -3515,25 +3864,25 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="D9" t="n">
-        <v>52.7</v>
+        <v>48.7</v>
       </c>
       <c r="E9" t="n">
-        <v>12.5</v>
+        <v>9.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G9" t="n">
-        <v>26.7</v>
+        <v>25.9</v>
       </c>
       <c r="H9" t="n">
         <v>40</v>
@@ -3542,50 +3891,50 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>13.8</v>
+        <v>20.9</v>
       </c>
       <c r="K9" t="n">
-        <v>-26.7</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>59.1</v>
       </c>
       <c r="D10" t="n">
-        <v>56.3</v>
+        <v>55.9</v>
       </c>
       <c r="E10" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="F10" t="n">
-        <v>38.5</v>
+        <v>34.6</v>
       </c>
       <c r="G10" t="n">
-        <v>11.8</v>
+        <v>15.2</v>
       </c>
       <c r="H10" t="n">
-        <v>58.3</v>
+        <v>51.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>18</v>
+        <v>20.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -3618,7 +3967,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -3653,7 +4002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -3686,858 +4035,864 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>72.9</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>64.9</v>
       </c>
       <c r="E14" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>38.1</v>
+        <v>48.1</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>52.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>18.3</v>
+        <v>24.3</v>
       </c>
       <c r="K14" t="n">
-        <v>10.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D15" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15"/>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>65.8</v>
+        <v>48.6</v>
       </c>
       <c r="E16" t="n">
-        <v>12.1</v>
+        <v>5.3</v>
       </c>
       <c r="F16" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>11.1</v>
+        <v>23.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>76.8</v>
       </c>
       <c r="D17" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="E17" t="n">
-        <v>9.1</v>
+        <v>13.6</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="G17" t="n">
-        <v>16.7</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7.7</v>
+        <v>15.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-16.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="G18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="D19" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>21.1</v>
+        <v>18.2</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.6</v>
+        <v>16.7</v>
       </c>
       <c r="H19" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>27</v>
+        <v>22.2</v>
       </c>
       <c r="K19" t="n">
-        <v>27.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="D20" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H20" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="K20" t="n">
-        <v>-16.7</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>33.3</v>
+        <v>51.4</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>59.4</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="H21" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22"/>
+        <v>28.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="D23" t="n">
-        <v>22.2</v>
+        <v>57.1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23"/>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K23" t="n">
-        <v>-50</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C24" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="D24" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C25" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="D25" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>9.3</v>
       </c>
       <c r="F25" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="H25" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>19.2</v>
+        <v>23.3</v>
       </c>
       <c r="K25" t="n">
-        <v>6.6</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>62.8</v>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>57.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26"/>
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>41.7</v>
+      </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C27" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>57.8</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F27" t="n">
-        <v>41.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F27"/>
       <c r="G27" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C28" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="D28" t="n">
-        <v>87.5</v>
+        <v>37.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H28" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C29" t="n">
-        <v>69.2</v>
+        <v>71.4</v>
       </c>
       <c r="D29" t="n">
-        <v>74.7</v>
+        <v>70.2</v>
       </c>
       <c r="E29" t="n">
-        <v>28.6</v>
+        <v>23.5</v>
       </c>
       <c r="F29" t="n">
         <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>57.9</v>
+        <v>40</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>24.4</v>
+        <v>34.8</v>
       </c>
       <c r="K29" t="n">
-        <v>19.3</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C30" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="D30" t="n">
-        <v>63.2</v>
+        <v>66.7</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>15.4</v>
+        <v>6.7</v>
       </c>
       <c r="H30" t="n">
-        <v>66.7</v>
+        <v>18.2</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>21.4</v>
+        <v>19.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C31" t="n">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>65.3</v>
+        <v>80</v>
       </c>
       <c r="E31" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="F31" t="n">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F31"/>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D32" t="n">
-        <v>41.2</v>
+        <v>57.8</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="H32" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-20</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C33" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="D33" t="n">
-        <v>44.1</v>
+        <v>87.5</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>-14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>69.2</v>
       </c>
       <c r="D34" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H34" t="n">
         <v>57.9</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>25</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>28.6</v>
+        <v>24.4</v>
       </c>
       <c r="K34" t="n">
-        <v>-25</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C35" t="n">
-        <v>58.1</v>
+        <v>61.5</v>
       </c>
       <c r="D35" t="n">
-        <v>60.9</v>
+        <v>63.2</v>
       </c>
       <c r="E35" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>71.4</v>
+        <v>30.8</v>
       </c>
       <c r="G35" t="n">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="H35" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="K35" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>65.3</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36"/>
+        <v>31.4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25</v>
+      </c>
       <c r="G36" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K36" t="n">
-        <v>-66.7</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C37" t="n">
-        <v>77.8</v>
+        <v>40</v>
       </c>
       <c r="D37" t="n">
-        <v>63.4</v>
+        <v>41.2</v>
       </c>
       <c r="E37" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>27.8</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C38" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="D38" t="n">
-        <v>31.6</v>
+        <v>44.1</v>
       </c>
       <c r="E38" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="G38" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -4546,40 +4901,213 @@
         <v>33.3</v>
       </c>
       <c r="K38" t="n">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="n">
+        <v>50</v>
+      </c>
+      <c r="D39" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>25</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="G40" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H40" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41"/>
+      <c r="G41" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-66.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" t="n">
+        <v>40</v>
+      </c>
+      <c r="D43" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" t="n">
+        <v>40</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K43" t="n">
         <v>-20</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39"/>
-      <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D39" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="E39" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F39" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G39" t="n">
+    <row r="44">
+      <c r="A44"/>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="G44" t="n">
         <v>15.1</v>
       </c>
-      <c r="H39" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>16</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-5.2</v>
+      <c r="H44" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-3.5</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -261,7 +261,7 @@
     <t xml:space="preserve">Trent Sillett</t>
   </si>
   <si>
-    <t xml:space="preserve">Ashton Abols</t>
+    <t xml:space="preserve">Ash Abols</t>
   </si>
   <si>
     <t xml:space="preserve">Wilfrid Laurier Golden Hawks</t>
@@ -282,7 +282,7 @@
     <t xml:space="preserve">Jack Symington</t>
   </si>
   <si>
-    <t xml:space="preserve">John Banks</t>
+    <t xml:space="preserve">Johnny Banks</t>
   </si>
   <si>
     <t xml:space="preserve">Lucas Bateman</t>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Tobey Drennan</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexander Pieper</t>
+    <t xml:space="preserve">Alex Peiper</t>
   </si>
   <si>
     <t xml:space="preserve">Guelph Gryphons</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Sawyer Whitaker</t>
   </si>
   <si>
-    <t xml:space="preserve">Thomas Cullen</t>
+    <t xml:space="preserve">Tommy Cullen</t>
   </si>
   <si>
     <t xml:space="preserve">Anden Cooper</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Declan Shannon</t>
   </si>
   <si>
-    <t xml:space="preserve">Edward Cheng</t>
+    <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
   </si>
   <si>
     <t xml:space="preserve">Eli Oughton</t>
@@ -204,7 +204,7 @@
     <t xml:space="preserve">Jai Pawa</t>
   </si>
   <si>
-    <t xml:space="preserve">Jun Yuki</t>
+    <t xml:space="preserve">Junichi Yuki</t>
   </si>
   <si>
     <t xml:space="preserve">Luca Valvo</t>
@@ -234,7 +234,7 @@
     <t xml:space="preserve">Western Mustangs</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexander Brown</t>
+    <t xml:space="preserve">Alex Brown</t>
   </si>
   <si>
     <t xml:space="preserve">Blake Conners</t>
@@ -799,7 +799,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -207,196 +207,196 @@
     <t xml:space="preserve">Junichi Yuki</t>
   </si>
   <si>
+    <t xml:space="preserve">Max Greaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Todd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nico Valvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhys Jenkyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Shephard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Awrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Mustangs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Conners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colin Mayhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ewan Ferguson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Hawke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koby Sernick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parker McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Nuernberger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Sillett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ash Abols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilfrid Laurier Golden Hawks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brady Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Boys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davis Llewellyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Larmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Symington</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnny Banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Bateman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Dineen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preston Vieira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">League Average:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FPS %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strike %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaway %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-BB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie Hughes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dante Cifala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drew McArthur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cohen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Tiessen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Palmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RJ Moniz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rowan Gelder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Facchini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson Michel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre Picard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Meron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J.C. Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landon Hutar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Miziolek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Rutherford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhys Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Van Raay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erik Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaden Fonseca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcello Colucci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neal Bhattacharya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McMillan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seth Cabezas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taio Fotiou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidan Armitage</t>
+  </si>
+  <si>
     <t xml:space="preserve">Luca Valvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Greaves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Todd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nico Valvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhys Jenkyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Shephard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Awrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Western Mustangs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Conners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colin Mayhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ewan Ferguson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Hawke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koby Sernick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parker McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Nuernberger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Sillett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ash Abols</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilfrid Laurier Golden Hawks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brady Hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Boys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davis Llewellyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Larmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Symington</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johnny Banks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Bateman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Dineen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preston Vieira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">League Average:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FPS %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strike %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaway %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K-BB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Hughes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dante Cifala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drew McArthur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cohen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Tiessen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Palmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RJ Moniz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rowan Gelder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Facchini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilson Michel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre Picard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Meron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J.C. Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landon Hutar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Miziolek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Rutherford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhys Montgomery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Van Raay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erik Lopez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaden Fonseca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcello Colucci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neal Bhattacharya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McMillan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seth Cabezas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taio Fotiou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidan Armitage</t>
   </si>
   <si>
     <t xml:space="preserve">Justin Stonkus</t>
@@ -478,8 +478,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K79" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K78" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K78"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -2550,31 +2550,31 @@
         <v>58</v>
       </c>
       <c r="C51" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
@@ -2585,31 +2585,31 @@
         <v>58</v>
       </c>
       <c r="C52" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E52" t="n">
-        <v>100</v>
+        <v>43.3</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G52" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2620,31 +2620,31 @@
         <v>58</v>
       </c>
       <c r="C53" t="n">
-        <v>60</v>
+        <v>58.8</v>
       </c>
       <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>10</v>
+      </c>
+      <c r="H53" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J53" t="n">
         <v>16.7</v>
       </c>
-      <c r="E53" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="F53" t="n">
+      <c r="K53" t="n">
         <v>16.7</v>
-      </c>
-      <c r="G53" t="n">
-        <v>20</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="n">
-        <v>50</v>
-      </c>
-      <c r="J53" t="n">
-        <v>50</v>
-      </c>
-      <c r="K53" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -2655,31 +2655,31 @@
         <v>58</v>
       </c>
       <c r="C54" t="n">
-        <v>53.8</v>
+        <v>83.3</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E54" t="n">
-        <v>53.8</v>
+        <v>66.6</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G54" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="H54" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="I54" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2690,31 +2690,31 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="D55" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="E55" t="n">
-        <v>66.6</v>
+        <v>72.7</v>
       </c>
       <c r="F55" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="G55" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56">
@@ -2725,98 +2725,98 @@
         <v>58</v>
       </c>
       <c r="C56" t="n">
-        <v>81.8</v>
+        <v>66.7</v>
       </c>
       <c r="D56" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G56" t="n">
         <v>9.1</v>
       </c>
-      <c r="E56" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="F56" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="I56" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J56" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="B57" t="s">
         <v>58</v>
       </c>
       <c r="C57" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>58.4</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2824,37 +2824,37 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" t="s">
         <v>71</v>
       </c>
-      <c r="B59" t="s">
-        <v>72</v>
-      </c>
       <c r="C59" t="n">
-        <v>61.5</v>
+        <v>85.7</v>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="E59" t="n">
-        <v>50.4</v>
+        <v>63.5</v>
       </c>
       <c r="F59" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="G59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H59" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J59" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
@@ -2862,34 +2862,34 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C60" t="n">
-        <v>85.7</v>
+        <v>88.9</v>
       </c>
       <c r="D60" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>63.5</v>
+        <v>88.9</v>
       </c>
       <c r="F60" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I60" t="n">
-        <v>33.3</v>
+        <v>80</v>
       </c>
       <c r="J60" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -2897,34 +2897,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" t="n">
-        <v>88.9</v>
+        <v>78.6</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>88.9</v>
+        <v>78.6</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H61" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2932,34 +2932,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" t="n">
-        <v>78.6</v>
+        <v>64.3</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>78.6</v>
+        <v>64.3</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I62" t="n">
-        <v>85.7</v>
+        <v>40</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
@@ -2967,34 +2967,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" t="n">
-        <v>64.3</v>
+        <v>80</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E63" t="n">
-        <v>64.3</v>
+        <v>55</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G63" t="n">
         <v>11.1</v>
       </c>
       <c r="H63" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="J63" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="K63" t="n">
-        <v>60</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="64">
@@ -3002,34 +3002,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" t="n">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="D64" t="n">
         <v>25</v>
       </c>
       <c r="E64" t="n">
-        <v>55</v>
+        <v>60.7</v>
       </c>
       <c r="F64" t="n">
         <v>25</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I64" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J64" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3037,34 +3037,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" t="n">
-        <v>85.7</v>
+        <v>90.9</v>
       </c>
       <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>50</v>
+      </c>
+      <c r="J65" t="n">
         <v>25</v>
       </c>
-      <c r="E65" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="F65" t="n">
-        <v>25</v>
-      </c>
-      <c r="G65" t="n">
-        <v>25</v>
-      </c>
-      <c r="H65" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I65" t="n">
-        <v>50</v>
-      </c>
-      <c r="J65" t="n">
-        <v>50</v>
-      </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="66">
@@ -3072,34 +3072,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C66" t="n">
-        <v>90.9</v>
+        <v>77.8</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E66" t="n">
-        <v>90.9</v>
+        <v>61.1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I66" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J66" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K66" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="67">
@@ -3107,34 +3107,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" t="n">
-        <v>77.8</v>
+        <v>85.7</v>
       </c>
       <c r="D67" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E67" t="n">
-        <v>61.1</v>
+        <v>66.9</v>
       </c>
       <c r="F67" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="G67" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="H67" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="I67" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="J67" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -3142,69 +3142,69 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C68" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="D68" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="E68" t="n">
-        <v>66.9</v>
+        <v>52.4</v>
       </c>
       <c r="F68" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="G68" t="n">
-        <v>6.7</v>
+        <v>35.7</v>
       </c>
       <c r="H68" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I68" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K68" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" t="s">
         <v>82</v>
       </c>
-      <c r="B69" t="s">
-        <v>83</v>
-      </c>
       <c r="C69" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D69" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="E69" t="n">
-        <v>52.4</v>
+        <v>33.4</v>
       </c>
       <c r="F69" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="G69" t="n">
-        <v>35.7</v>
+        <v>42.9</v>
       </c>
       <c r="H69" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3212,25 +3212,25 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C70" t="n">
-        <v>55.6</v>
+        <v>77.8</v>
       </c>
       <c r="D70" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="E70" t="n">
-        <v>33.4</v>
+        <v>63.5</v>
       </c>
       <c r="F70" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="G70" t="n">
-        <v>42.9</v>
+        <v>43.8</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I70" t="n">
         <v>100</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="71">
@@ -3247,34 +3247,34 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C71" t="n">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="D71" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="E71" t="n">
-        <v>63.5</v>
+        <v>66.7</v>
       </c>
       <c r="F71" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="G71" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K71" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="72">
@@ -3282,34 +3282,34 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="D72" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="F72" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I72" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J72" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73">
@@ -3317,34 +3317,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C73" t="n">
-        <v>57.1</v>
+        <v>70</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E73" t="n">
-        <v>57.1</v>
+        <v>32.5</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="G73" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J73" t="n">
         <v>25</v>
       </c>
-      <c r="H73" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I73" t="n">
-        <v>60</v>
-      </c>
-      <c r="J73" t="n">
-        <v>20</v>
-      </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
@@ -3352,34 +3352,34 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C74" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D74" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>32.5</v>
+        <v>100</v>
       </c>
       <c r="F74" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>37.5</v>
+        <v>55.6</v>
       </c>
       <c r="J74" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="K74" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="75">
@@ -3387,34 +3387,34 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C75" t="n">
-        <v>100</v>
+        <v>81.2</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>100</v>
+        <v>71.2</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G75" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>55.6</v>
+        <v>28.6</v>
       </c>
       <c r="J75" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3422,31 +3422,31 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C76" t="n">
-        <v>81.2</v>
+        <v>90</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E76" t="n">
-        <v>71.2</v>
+        <v>73.3</v>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="G76" t="n">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3457,22 +3457,22 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>73.3</v>
+        <v>100</v>
       </c>
       <c r="F77" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3481,78 +3481,43 @@
         <v>33.3</v>
       </c>
       <c r="J77" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78"/>
+      <c r="B78" t="s">
         <v>92</v>
       </c>
-      <c r="B78" t="s">
-        <v>83</v>
-      </c>
       <c r="C78" t="n">
-        <v>100</v>
+        <v>69.5</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="E78" t="n">
-        <v>100</v>
+        <v>54.6</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="I78" t="n">
-        <v>33.3</v>
+        <v>51.4</v>
       </c>
       <c r="J78" t="n">
-        <v>33.3</v>
+        <v>22.8</v>
       </c>
       <c r="K78" t="n">
-        <v>33.3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79"/>
-      <c r="B79" t="s">
-        <v>93</v>
-      </c>
-      <c r="C79" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="D79" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E79" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="F79" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G79" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="H79" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="I79" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="J79" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K79" t="n">
-        <v>31.3</v>
+        <v>31.7</v>
       </c>
     </row>
   </sheetData>
@@ -3584,22 +3549,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -3608,13 +3573,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
@@ -3689,7 +3654,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -3724,7 +3689,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -3759,7 +3724,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -3794,7 +3759,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -3864,7 +3829,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -3899,7 +3864,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -3934,7 +3899,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -3967,7 +3932,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -4002,7 +3967,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -4035,7 +4000,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -4070,7 +4035,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -4105,7 +4070,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
@@ -4140,7 +4105,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
@@ -4175,7 +4140,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -4210,7 +4175,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
@@ -4245,7 +4210,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
@@ -4280,7 +4245,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -4315,7 +4280,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -4350,7 +4315,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
@@ -4385,7 +4350,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
@@ -4420,7 +4385,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
@@ -4455,7 +4420,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
@@ -4490,7 +4455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
@@ -4523,7 +4488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B28" t="s">
         <v>42</v>
@@ -4558,7 +4523,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
         <v>42</v>
@@ -4593,7 +4558,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B30" t="s">
         <v>42</v>
@@ -4628,7 +4593,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s">
         <v>42</v>
@@ -4661,7 +4626,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" t="s">
         <v>58</v>
@@ -4696,7 +4661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -4731,7 +4696,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>58</v>
@@ -4769,7 +4734,7 @@
         <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C35" t="n">
         <v>61.5</v>
@@ -4804,7 +4769,7 @@
         <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C36" t="n">
         <v>58.3</v>
@@ -4839,7 +4804,7 @@
         <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C37" t="n">
         <v>40</v>
@@ -4874,7 +4839,7 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" t="n">
         <v>14.3</v>
@@ -4909,7 +4874,7 @@
         <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C39" t="n">
         <v>50</v>
@@ -4944,7 +4909,7 @@
         <v>133</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C40" t="n">
         <v>58.1</v>
@@ -4979,7 +4944,7 @@
         <v>134</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -5012,7 +4977,7 @@
         <v>135</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C42" t="n">
         <v>77.8</v>
@@ -5047,7 +5012,7 @@
         <v>136</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C43" t="n">
         <v>40</v>
@@ -5080,7 +5045,7 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" t="n">
         <v>56.5</v>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Gavin Taylor</t>
   </si>
   <si>
-    <t xml:space="preserve">Hayden Cupolo</t>
+    <t xml:space="preserve">Haydon Cupolo</t>
   </si>
   <si>
     <t xml:space="preserve">Jaden Leeder</t>
@@ -345,7 +345,7 @@
     <t xml:space="preserve">Wilson Michel</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexandre Picard</t>
+    <t xml:space="preserve">Alex Picard</t>
   </si>
   <si>
     <t xml:space="preserve">Daniel Meron</t>
@@ -369,7 +369,7 @@
     <t xml:space="preserve">Rhys Montgomery</t>
   </si>
   <si>
-    <t xml:space="preserve">Alex Van Raay</t>
+    <t xml:space="preserve">Alex VanRaay</t>
   </si>
   <si>
     <t xml:space="preserve">Erik Lopez</t>
@@ -381,7 +381,7 @@
     <t xml:space="preserve">Marcello Colucci</t>
   </si>
   <si>
-    <t xml:space="preserve">Neal Bhattacharya</t>
+    <t xml:space="preserve">Neal (Amar) Bhattacharya</t>
   </si>
   <si>
     <t xml:space="preserve">Sam McMillan</t>
@@ -408,7 +408,7 @@
     <t xml:space="preserve">21</t>
   </si>
   <si>
-    <t xml:space="preserve">Benjamin Rae</t>
+    <t xml:space="preserve">Ben Rae</t>
   </si>
   <si>
     <t xml:space="preserve">Bryson Kraan</t>
@@ -3534,7 +3534,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="5.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
@@ -3754,7 +3754,7 @@
         <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3894,7 +3894,7 @@
         <v>20.9</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4553,7 +4553,7 @@
         <v>34.8</v>
       </c>
       <c r="K29" t="n">
-        <v>21.4</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="30">
@@ -5072,7 +5072,7 @@
         <v>19.2</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -66,6 +66,9 @@
     <t xml:space="preserve">Cole Carpenter</t>
   </si>
   <si>
+    <t xml:space="preserve">Colin Mockford</t>
+  </si>
+  <si>
     <t xml:space="preserve">Flynn Matheson</t>
   </si>
   <si>
@@ -78,6 +81,15 @@
     <t xml:space="preserve">Jaden Leeder</t>
   </si>
   <si>
+    <t xml:space="preserve">Johnny Banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Frazer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kade Falardeau</t>
+  </si>
+  <si>
     <t xml:space="preserve">Liam Riley</t>
   </si>
   <si>
@@ -270,21 +282,45 @@
     <t xml:space="preserve">Brendan Boys</t>
   </si>
   <si>
+    <t xml:space="preserve">Cameron Bendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cole Geldart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Leonard</t>
+  </si>
+  <si>
     <t xml:space="preserve">Davis Llewellyn</t>
   </si>
   <si>
+    <t xml:space="preserve">Gabriel Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffen Duenkler</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jack Larmer</t>
   </si>
   <si>
     <t xml:space="preserve">Jack Symington</t>
   </si>
   <si>
-    <t xml:space="preserve">Johnny Banks</t>
+    <t xml:space="preserve">Jared Wellman</t>
   </si>
   <si>
     <t xml:space="preserve">Lucas Bateman</t>
   </si>
   <si>
+    <t xml:space="preserve">Matthew Kong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Goranson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Vieira</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peter Dineen</t>
   </si>
   <si>
@@ -324,6 +360,9 @@
     <t xml:space="preserve">Drew McArthur</t>
   </si>
   <si>
+    <t xml:space="preserve">Evan Marks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jack Cohen</t>
   </si>
   <si>
@@ -333,6 +372,12 @@
     <t xml:space="preserve">Joel Palmer</t>
   </si>
   <si>
+    <t xml:space="preserve">Max Van Dam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan McFarlane</t>
+  </si>
+  <si>
     <t xml:space="preserve">RJ Moniz</t>
   </si>
   <si>
@@ -411,16 +456,31 @@
     <t xml:space="preserve">Ben Rae</t>
   </si>
   <si>
+    <t xml:space="preserve">Benjamin Ondevilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bryson Kraan</t>
   </si>
   <si>
     <t xml:space="preserve">Gavin McLean</t>
   </si>
   <si>
+    <t xml:space="preserve">Jack Comper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Rosseti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Miller</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kyle Tamaki</t>
   </si>
   <si>
     <t xml:space="preserve">Liam Conlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattheo Tsebelis</t>
   </si>
   <si>
     <t xml:space="preserve">Nathan Mazer</t>
@@ -478,8 +538,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K78" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K91" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K91"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -498,8 +558,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K44" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K54" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K54"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -855,31 +915,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="E2" t="n">
-        <v>55.3</v>
+        <v>54.9</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="J2" t="n">
-        <v>28.6</v>
+        <v>24.2</v>
       </c>
       <c r="K2" t="n">
-        <v>46.4</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="3">
@@ -890,31 +950,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>76.1</v>
+        <v>76.7</v>
       </c>
       <c r="D3" t="n">
-        <v>10.2</v>
+        <v>15.1</v>
       </c>
       <c r="E3" t="n">
-        <v>65.9</v>
+        <v>61.6</v>
       </c>
       <c r="F3" t="n">
-        <v>10.2</v>
+        <v>15.1</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>38.9</v>
+        <v>38.1</v>
       </c>
       <c r="J3" t="n">
-        <v>30.6</v>
+        <v>31</v>
       </c>
       <c r="K3" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="4">
@@ -925,22 +985,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>39.3</v>
+        <v>41.4</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>36.4</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="I4" t="n">
         <v>57.1</v>
@@ -1029,32 +1089,24 @@
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
       <c r="G7" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>24.2</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1065,31 +1117,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>81.6</v>
+        <v>79.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="E8" t="n">
-        <v>81.6</v>
+        <v>56.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="G8" t="n">
-        <v>16.1</v>
+        <v>26.1</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>8.9</v>
       </c>
       <c r="I8" t="n">
         <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>31.2</v>
+        <v>26.3</v>
       </c>
       <c r="K8" t="n">
-        <v>62.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="9">
@@ -1100,25 +1152,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
-      </c>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
+        <v>75.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>40.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="10">
@@ -1129,31 +1187,25 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>67.4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>20</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
       <c r="G10" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>43.3</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1164,31 +1216,31 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>76.5</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="E11" t="n">
-        <v>62.2</v>
+        <v>49.1</v>
       </c>
       <c r="F11" t="n">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="G11" t="n">
-        <v>34.8</v>
+        <v>33.7</v>
       </c>
       <c r="H11" t="n">
-        <v>12.9</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>45.5</v>
       </c>
       <c r="J11" t="n">
-        <v>40</v>
+        <v>21.2</v>
       </c>
       <c r="K11" t="n">
-        <v>47.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="12">
@@ -1198,33 +1250,15 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="n">
-        <v>80</v>
-      </c>
-      <c r="D12" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -1234,31 +1268,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>80.8</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>16.5</v>
+        <v>7.1</v>
       </c>
       <c r="E13" t="n">
-        <v>64.3</v>
+        <v>67.9</v>
       </c>
       <c r="F13" t="n">
-        <v>16.5</v>
+        <v>7.1</v>
       </c>
       <c r="G13" t="n">
-        <v>26.9</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>11.1</v>
       </c>
       <c r="I13" t="n">
-        <v>39.5</v>
+        <v>42.9</v>
       </c>
       <c r="J13" t="n">
-        <v>31.6</v>
+        <v>28.6</v>
       </c>
       <c r="K13" t="n">
-        <v>32.4</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="14">
@@ -1269,31 +1303,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>55.4</v>
+        <v>57.9</v>
       </c>
       <c r="D14" t="n">
-        <v>14.9</v>
+        <v>9.5</v>
       </c>
       <c r="E14" t="n">
-        <v>40.5</v>
+        <v>48.4</v>
       </c>
       <c r="F14" t="n">
-        <v>14.9</v>
+        <v>9.5</v>
       </c>
       <c r="G14" t="n">
-        <v>11.8</v>
+        <v>23.1</v>
       </c>
       <c r="H14" t="n">
-        <v>13.5</v>
+        <v>22.2</v>
       </c>
       <c r="I14" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>21.2</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -1304,31 +1338,31 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>76.5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>62.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I15" t="n">
-        <v>16.7</v>
+        <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>83.3</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>33.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="16">
@@ -1336,124 +1370,124 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>69.7</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>26.1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>66.7</v>
+        <v>79</v>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.9</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="F17" t="n">
-        <v>16.7</v>
+        <v>17.9</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>24.3</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>1.8</v>
       </c>
       <c r="I17" t="n">
-        <v>75</v>
+        <v>38.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>86.7</v>
+        <v>55.4</v>
       </c>
       <c r="D18" t="n">
-        <v>9.1</v>
+        <v>14.9</v>
       </c>
       <c r="E18" t="n">
-        <v>77.6</v>
+        <v>40.5</v>
       </c>
       <c r="F18" t="n">
-        <v>9.1</v>
+        <v>14.9</v>
       </c>
       <c r="G18" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="H18" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="I18" t="n">
-        <v>62.5</v>
+        <v>51.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="K18" t="n">
-        <v>12.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1462,48 +1496,48 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
         <v>31</v>
       </c>
-      <c r="B20" t="s">
-        <v>27</v>
-      </c>
       <c r="C20" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>52.5</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>20.8</v>
+        <v>50</v>
       </c>
       <c r="H20" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1511,34 +1545,34 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>82.1</v>
+        <v>66.7</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="n">
-        <v>62.1</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G21" t="n">
-        <v>21.4</v>
+        <v>50</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I21" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="J21" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
@@ -1546,34 +1580,34 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>76</v>
+        <v>86.7</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>77.6</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="G22" t="n">
-        <v>31.8</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I22" t="n">
-        <v>33.3</v>
+        <v>62.5</v>
       </c>
       <c r="J22" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="23">
@@ -1581,34 +1615,34 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>71.9</v>
+        <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E23" t="n">
-        <v>67.9</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G23" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1616,34 +1650,34 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>84</v>
+        <v>62.5</v>
       </c>
       <c r="D24" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>78.4</v>
+        <v>52.5</v>
       </c>
       <c r="F24" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>4.5</v>
+        <v>20.8</v>
       </c>
       <c r="H24" t="n">
-        <v>11.8</v>
+        <v>17.6</v>
       </c>
       <c r="I24" t="n">
-        <v>26.7</v>
+        <v>9.1</v>
       </c>
       <c r="J24" t="n">
-        <v>40</v>
+        <v>54.5</v>
       </c>
       <c r="K24" t="n">
-        <v>46.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="25">
@@ -1651,34 +1685,34 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>59.3</v>
+        <v>82.1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.1</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>50.2</v>
+        <v>62.1</v>
       </c>
       <c r="F25" t="n">
-        <v>9.1</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>42.1</v>
+        <v>21.4</v>
       </c>
       <c r="H25" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>33.3</v>
+        <v>53.8</v>
       </c>
       <c r="J25" t="n">
-        <v>50</v>
+        <v>15.4</v>
       </c>
       <c r="K25" t="n">
-        <v>16.7</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="26">
@@ -1686,34 +1720,34 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I26" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="27">
@@ -1721,34 +1755,34 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C27" t="n">
-        <v>63.6</v>
+        <v>71.9</v>
       </c>
       <c r="D27" t="n">
-        <v>22.2</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>41.4</v>
+        <v>67.9</v>
       </c>
       <c r="F27" t="n">
-        <v>22.2</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H27" t="n">
         <v>11.1</v>
       </c>
-      <c r="H27" t="n">
-        <v>12.5</v>
-      </c>
       <c r="I27" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -1756,34 +1790,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>48.6</v>
+        <v>84</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="E28" t="n">
-        <v>40.6</v>
+        <v>78.4</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="G28" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="H28" t="n">
-        <v>7.1</v>
+        <v>11.8</v>
       </c>
       <c r="I28" t="n">
-        <v>55.6</v>
+        <v>26.7</v>
       </c>
       <c r="J28" t="n">
-        <v>22.2</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>22.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="29">
@@ -1791,34 +1825,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>56.2</v>
+        <v>59.3</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>9.1</v>
       </c>
       <c r="E29" t="n">
-        <v>26.2</v>
+        <v>50.2</v>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>9.1</v>
       </c>
       <c r="G29" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I29" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30">
@@ -1826,7 +1860,7 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C30" t="n">
         <v>50</v>
@@ -1841,16 +1875,16 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1858,142 +1892,142 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C31" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>41.4</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G31" t="n">
-        <v>26.7</v>
+        <v>11.1</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="I31" t="n">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="J31" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>48.6</v>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>27.5</v>
+        <v>40.6</v>
       </c>
       <c r="F32" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I32" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>47.1</v>
+        <v>56.2</v>
       </c>
       <c r="D33" t="n">
-        <v>16.7</v>
+        <v>30</v>
       </c>
       <c r="E33" t="n">
-        <v>30.4</v>
+        <v>26.2</v>
       </c>
       <c r="F33" t="n">
-        <v>16.7</v>
+        <v>30</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="J33" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s">
         <v>46</v>
       </c>
-      <c r="B34" t="s">
-        <v>42</v>
-      </c>
       <c r="C34" t="n">
+        <v>50</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
         <v>66.7</v>
       </c>
-      <c r="D34" t="n">
-        <v>25</v>
-      </c>
-      <c r="E34" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F34" t="n">
-        <v>25</v>
-      </c>
-      <c r="G34" t="n">
-        <v>25</v>
-      </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2001,31 +2035,31 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C35" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>67.5</v>
+        <v>60</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>37.5</v>
+        <v>26.7</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
-        <v>33.3</v>
+        <v>83.3</v>
       </c>
       <c r="J35" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="K35" t="n">
         <v>66.7</v>
@@ -2036,61 +2070,69 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36"/>
+        <v>12.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
         <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C37" t="n">
-        <v>57.7</v>
+        <v>47.1</v>
       </c>
       <c r="D37" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="E37" t="n">
-        <v>40.1</v>
+        <v>30.4</v>
       </c>
       <c r="F37" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="G37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>45.5</v>
+        <v>57.1</v>
       </c>
       <c r="J37" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
       </c>
       <c r="K37" t="n">
-        <v>45.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="38">
@@ -2098,28 +2140,28 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2133,31 +2175,31 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="E39" t="n">
-        <v>42.3</v>
+        <v>67.5</v>
       </c>
       <c r="F39" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="G39" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K39" t="n">
         <v>66.7</v>
@@ -2168,69 +2210,61 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C40" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" t="n">
-        <v>25</v>
-      </c>
+      <c r="G40"/>
       <c r="H40" t="n">
         <v>0</v>
       </c>
-      <c r="I40" t="n">
-        <v>50</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>50</v>
-      </c>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C41" t="n">
-        <v>55.6</v>
+        <v>57.7</v>
       </c>
       <c r="D41" t="n">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
       <c r="E41" t="n">
-        <v>41.3</v>
+        <v>40.1</v>
       </c>
       <c r="F41" t="n">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
       <c r="G41" t="n">
-        <v>38.5</v>
+        <v>5.6</v>
       </c>
       <c r="H41" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J41" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="K41" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="42">
@@ -2238,34 +2272,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C42" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
@@ -2273,22 +2307,22 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>36.4</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>70</v>
+        <v>7.7</v>
       </c>
       <c r="E43" t="n">
-        <v>-33.6</v>
+        <v>42.3</v>
       </c>
       <c r="F43" t="n">
-        <v>70</v>
+        <v>7.7</v>
       </c>
       <c r="G43" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2297,10 +2331,10 @@
         <v>66.7</v>
       </c>
       <c r="J43" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="44">
@@ -2308,34 +2342,34 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C44" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="D44" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>24</v>
+        <v>66.7</v>
       </c>
       <c r="F44" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -2343,31 +2377,31 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C45" t="n">
-        <v>53.8</v>
+        <v>55.6</v>
       </c>
       <c r="D45" t="n">
-        <v>45.5</v>
+        <v>14.3</v>
       </c>
       <c r="E45" t="n">
-        <v>8.3</v>
+        <v>41.3</v>
       </c>
       <c r="F45" t="n">
-        <v>45.5</v>
+        <v>14.3</v>
       </c>
       <c r="G45" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>50</v>
+      </c>
+      <c r="J45" t="n">
         <v>25</v>
-      </c>
-      <c r="H45" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I45" t="n">
-        <v>50</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>50</v>
@@ -2375,63 +2409,69 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C46" t="n">
-        <v>100</v>
-      </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
+        <v>66.7</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" t="n">
+        <v>16.7</v>
+      </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I46" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K46" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>78.6</v>
+        <v>36.4</v>
       </c>
       <c r="D47" t="n">
-        <v>36.4</v>
+        <v>70</v>
       </c>
       <c r="E47" t="n">
-        <v>42.2</v>
+        <v>-33.6</v>
       </c>
       <c r="F47" t="n">
-        <v>36.4</v>
+        <v>70</v>
       </c>
       <c r="G47" t="n">
-        <v>13.3</v>
+        <v>45.5</v>
       </c>
       <c r="H47" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J47" t="n">
         <v>33.3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>50</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2439,72 +2479,72 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>76.9</v>
+        <v>62.5</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>38.5</v>
       </c>
       <c r="E48" t="n">
-        <v>51.9</v>
+        <v>24</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>38.5</v>
       </c>
       <c r="G48" t="n">
-        <v>9.1</v>
+        <v>26.7</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>57.1</v>
+        <v>37.5</v>
       </c>
       <c r="J48" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="K48" t="n">
-        <v>42.9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
         <v>62</v>
       </c>
-      <c r="B49" t="s">
-        <v>58</v>
-      </c>
       <c r="C49" t="n">
-        <v>83.3</v>
+        <v>53.8</v>
       </c>
       <c r="D49" t="n">
-        <v>28.6</v>
+        <v>45.5</v>
       </c>
       <c r="E49" t="n">
-        <v>54.7</v>
+        <v>8.3</v>
       </c>
       <c r="F49" t="n">
-        <v>28.6</v>
+        <v>45.5</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H49" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J49" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -2512,34 +2552,28 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C50" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>25</v>
-      </c>
-      <c r="E50" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
       <c r="G50" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51">
@@ -2547,34 +2581,34 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C51" t="n">
-        <v>100</v>
+        <v>78.6</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="E51" t="n">
-        <v>100</v>
+        <v>42.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="G51" t="n">
-        <v>66.7</v>
+        <v>13.3</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I51" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2582,34 +2616,34 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C52" t="n">
-        <v>60</v>
+        <v>76.9</v>
       </c>
       <c r="D52" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E52" t="n">
-        <v>43.3</v>
+        <v>51.9</v>
       </c>
       <c r="F52" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G52" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K52" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="53">
@@ -2617,34 +2651,34 @@
         <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C53" t="n">
-        <v>58.8</v>
+        <v>83.3</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E53" t="n">
-        <v>58.8</v>
+        <v>54.7</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="I53" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2652,31 +2686,31 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C54" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="D54" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E54" t="n">
-        <v>66.6</v>
+        <v>32.1</v>
       </c>
       <c r="F54" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G54" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="H54" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2687,34 +2721,34 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C55" t="n">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="F55" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H55" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
@@ -2722,101 +2756,101 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C56" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="D56" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
       <c r="E56" t="n">
-        <v>58.4</v>
+        <v>43.3</v>
       </c>
       <c r="F56" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
       <c r="G56" t="n">
-        <v>9.1</v>
+        <v>20</v>
       </c>
       <c r="H56" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="I56" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J56" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C58" t="n">
-        <v>61.5</v>
+        <v>83.3</v>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E58" t="n">
-        <v>50.4</v>
+        <v>66.6</v>
       </c>
       <c r="F58" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>42.9</v>
       </c>
       <c r="H58" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="I58" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2827,34 +2861,34 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>85.7</v>
+        <v>81.8</v>
       </c>
       <c r="D59" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="E59" t="n">
-        <v>63.5</v>
+        <v>72.7</v>
       </c>
       <c r="F59" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>20</v>
+      </c>
+      <c r="I59" t="n">
+        <v>75</v>
+      </c>
+      <c r="J59" t="n">
         <v>25</v>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J59" t="n">
-        <v>33.3</v>
-      </c>
       <c r="K59" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60">
@@ -2862,63 +2896,63 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C60" t="n">
-        <v>88.9</v>
+        <v>66.7</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E60" t="n">
-        <v>88.9</v>
+        <v>58.4</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H60" t="n">
         <v>14.3</v>
       </c>
       <c r="I60" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K60" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C61" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2929,37 +2963,37 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" t="s">
         <v>75</v>
       </c>
-      <c r="B62" t="s">
-        <v>71</v>
-      </c>
       <c r="C62" t="n">
-        <v>64.3</v>
+        <v>61.5</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="n">
-        <v>64.3</v>
+        <v>50.4</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G62" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="H62" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="I62" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2967,34 +3001,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C63" t="n">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="D63" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G63" t="n">
         <v>25</v>
       </c>
-      <c r="E63" t="n">
-        <v>55</v>
-      </c>
-      <c r="F63" t="n">
-        <v>25</v>
-      </c>
-      <c r="G63" t="n">
-        <v>11.1</v>
-      </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="J63" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="K63" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -3002,34 +3036,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C64" t="n">
-        <v>85.7</v>
+        <v>88.9</v>
       </c>
       <c r="D64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>60.7</v>
+        <v>88.9</v>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -3037,34 +3071,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C65" t="n">
-        <v>90.9</v>
+        <v>78.6</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>90.9</v>
+        <v>78.6</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="J65" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3072,34 +3106,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C66" t="n">
-        <v>77.8</v>
+        <v>64.3</v>
       </c>
       <c r="D66" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>61.1</v>
+        <v>64.3</v>
       </c>
       <c r="F66" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>4.2</v>
+        <v>11.1</v>
       </c>
       <c r="H66" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="I66" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="J66" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67">
@@ -3107,34 +3141,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C67" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="D67" t="n">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="E67" t="n">
-        <v>66.9</v>
+        <v>55</v>
       </c>
       <c r="F67" t="n">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="G67" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J67" t="n">
         <v>14.3</v>
       </c>
-      <c r="I67" t="n">
-        <v>40</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
       <c r="K67" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="68">
@@ -3142,174 +3176,174 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C68" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="D68" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="E68" t="n">
-        <v>52.4</v>
+        <v>60.7</v>
       </c>
       <c r="F68" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="G68" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
       <c r="H68" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="I68" t="n">
         <v>50</v>
       </c>
       <c r="J68" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K68" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C69" t="n">
-        <v>55.6</v>
+        <v>90.9</v>
       </c>
       <c r="D69" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>33.4</v>
+        <v>90.9</v>
       </c>
       <c r="F69" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C70" t="n">
         <v>77.8</v>
       </c>
       <c r="D70" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E70" t="n">
-        <v>63.5</v>
+        <v>61.1</v>
       </c>
       <c r="F70" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="G70" t="n">
-        <v>43.8</v>
+        <v>4.2</v>
       </c>
       <c r="H70" t="n">
-        <v>28.6</v>
+        <v>11.1</v>
       </c>
       <c r="I70" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K70" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C71" t="n">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="D71" t="n">
-        <v>8.3</v>
+        <v>18.8</v>
       </c>
       <c r="E71" t="n">
-        <v>66.7</v>
+        <v>66.9</v>
       </c>
       <c r="F71" t="n">
-        <v>8.3</v>
+        <v>18.8</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I71" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J71" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72" t="s">
         <v>86</v>
       </c>
-      <c r="B72" t="s">
-        <v>82</v>
-      </c>
       <c r="C72" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E72" t="n">
-        <v>57.1</v>
+        <v>52.4</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G72" t="n">
-        <v>25</v>
+        <v>35.7</v>
       </c>
       <c r="H72" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I72" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J72" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K72" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="73">
@@ -3317,34 +3351,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C73" t="n">
-        <v>70</v>
+        <v>55.6</v>
       </c>
       <c r="D73" t="n">
-        <v>37.5</v>
+        <v>22.2</v>
       </c>
       <c r="E73" t="n">
-        <v>32.5</v>
+        <v>33.4</v>
       </c>
       <c r="F73" t="n">
-        <v>37.5</v>
+        <v>22.2</v>
       </c>
       <c r="G73" t="n">
-        <v>17.6</v>
+        <v>42.9</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="J73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3352,34 +3386,34 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C74" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="E74" t="n">
-        <v>100</v>
+        <v>62.6</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G74" t="n">
-        <v>16.7</v>
+        <v>36</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I74" t="n">
-        <v>55.6</v>
+        <v>62.5</v>
       </c>
       <c r="J74" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="K74" t="n">
-        <v>22.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
@@ -3387,22 +3421,22 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C75" t="n">
-        <v>81.2</v>
+        <v>91.7</v>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E75" t="n">
-        <v>71.2</v>
+        <v>41.7</v>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G75" t="n">
-        <v>14.3</v>
+        <v>21.4</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3411,10 +3445,10 @@
         <v>28.6</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="76">
@@ -3422,31 +3456,31 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C76" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D76" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3457,67 +3491,522 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C77" t="n">
         <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E77" t="n">
+        <v>80</v>
+      </c>
+      <c r="F77" t="n">
+        <v>20</v>
+      </c>
+      <c r="G77" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" t="n">
+        <v>75</v>
+      </c>
+      <c r="D78" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>50</v>
+      </c>
+      <c r="J78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" t="n">
         <v>100</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>100</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>100</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F80" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
         <v>33.3</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J80" t="n">
         <v>33.3</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K80" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>95</v>
+      </c>
+      <c r="B81" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>25</v>
+      </c>
+      <c r="H81" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>60</v>
+      </c>
+      <c r="J81" t="n">
+        <v>20</v>
+      </c>
+      <c r="K81" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>96</v>
+      </c>
+      <c r="B82" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" t="n">
+        <v>70</v>
+      </c>
+      <c r="D82" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E82" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F82" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J82" t="n">
+        <v>25</v>
+      </c>
+      <c r="K82" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>97</v>
+      </c>
+      <c r="B83" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" t="n">
+        <v>75</v>
+      </c>
+      <c r="D83" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E83" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F83" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G83" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I83" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84" t="n">
+        <v>84.6</v>
+      </c>
+      <c r="D84" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>13</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="J84" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K84" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" t="n">
+        <v>68.6</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I85" t="n">
         <v>33.3</v>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78"/>
-      <c r="B78" t="s">
-        <v>92</v>
-      </c>
-      <c r="C78" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="D78" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E78" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="F78" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I78" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="J78" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K78" t="n">
-        <v>31.7</v>
+      <c r="J85" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K85" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="n">
+        <v>50</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>50</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D87" t="n">
+        <v>20</v>
+      </c>
+      <c r="E87" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="F87" t="n">
+        <v>20</v>
+      </c>
+      <c r="G87" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J87" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K87" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" t="s">
+        <v>86</v>
+      </c>
+      <c r="C88" t="n">
+        <v>60</v>
+      </c>
+      <c r="D88" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E88" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G88" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H88" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>100</v>
+      </c>
+      <c r="K88" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>102</v>
+      </c>
+      <c r="B89" t="s">
+        <v>86</v>
+      </c>
+      <c r="C89" t="n">
+        <v>90</v>
+      </c>
+      <c r="D89" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E89" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G89" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>50</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>103</v>
+      </c>
+      <c r="B90" t="s">
+        <v>86</v>
+      </c>
+      <c r="C90" t="n">
+        <v>100</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>100</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91"/>
+      <c r="B91" t="s">
+        <v>104</v>
+      </c>
+      <c r="C91" t="n">
+        <v>70.1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E91" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G91" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I91" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="K91" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3549,22 +4038,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -3573,13 +4062,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2">
@@ -3654,42 +4143,42 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>53.9</v>
+        <v>58.1</v>
       </c>
       <c r="D4" t="n">
-        <v>65.4</v>
+        <v>66.8</v>
       </c>
       <c r="E4" t="n">
-        <v>16.5</v>
+        <v>19.3</v>
       </c>
       <c r="F4" t="n">
-        <v>33.3</v>
+        <v>36.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H4" t="n">
-        <v>54.3</v>
+        <v>51.1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -3724,7 +4213,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -3759,7 +4248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -3794,137 +4283,139 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>66.7</v>
+        <v>92.9</v>
       </c>
       <c r="D8" t="n">
-        <v>70.6</v>
+        <v>87.1</v>
       </c>
       <c r="E8" t="n">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="D9" t="n">
-        <v>48.7</v>
+        <v>70.6</v>
       </c>
       <c r="E9" t="n">
-        <v>9.2</v>
+        <v>28.6</v>
       </c>
       <c r="F9" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>20.9</v>
+        <v>9.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-18.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>59.1</v>
+        <v>57.1</v>
       </c>
       <c r="D10" t="n">
-        <v>55.9</v>
+        <v>48.7</v>
       </c>
       <c r="E10" t="n">
-        <v>10.2</v>
+        <v>9.2</v>
       </c>
       <c r="F10" t="n">
-        <v>34.6</v>
+        <v>16.7</v>
       </c>
       <c r="G10" t="n">
-        <v>15.2</v>
+        <v>25.9</v>
       </c>
       <c r="H10" t="n">
-        <v>51.2</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>20.9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>59.1</v>
       </c>
       <c r="D11" t="n">
-        <v>66.7</v>
+        <v>55.9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11"/>
+        <v>10.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>34.6</v>
+      </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -3932,536 +4423,534 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>53.3</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>43.6</v>
+        <v>66.7</v>
       </c>
       <c r="E12" t="n">
-        <v>8.8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F12"/>
       <c r="G12" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
         <v>33.3</v>
       </c>
-      <c r="D13" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
-        <v>100</v>
-      </c>
-      <c r="H13"/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>53.3</v>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-100</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>64.9</v>
+        <v>61.1</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="F14" t="n">
-        <v>48.1</v>
+        <v>33.3</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>24.3</v>
+        <v>14.3</v>
       </c>
       <c r="K14" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>33.3</v>
+        <v>53.3</v>
       </c>
       <c r="D15" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" t="n">
         <v>35.7</v>
       </c>
-      <c r="E15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>16.7</v>
       </c>
-      <c r="H15" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20</v>
-      </c>
       <c r="K15" t="n">
-        <v>-16.7</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>33.3</v>
       </c>
       <c r="D16" t="n">
-        <v>48.6</v>
+        <v>36.8</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H16"/>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>23.1</v>
+        <v>16.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-10</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>76.8</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>66.7</v>
+        <v>64.9</v>
       </c>
       <c r="E17" t="n">
-        <v>13.6</v>
+        <v>21</v>
       </c>
       <c r="F17" t="n">
-        <v>44.4</v>
+        <v>48.1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H17" t="n">
-        <v>47.7</v>
+        <v>52.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>15.7</v>
+        <v>24.3</v>
       </c>
       <c r="K17" t="n">
-        <v>8.9</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="D18" t="n">
-        <v>57.5</v>
+        <v>35.7</v>
       </c>
       <c r="E18" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="H18" t="n">
-        <v>54.5</v>
+        <v>33.3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>83.3</v>
+        <v>70</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>48.6</v>
       </c>
       <c r="E19" t="n">
-        <v>18.2</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>37.5</v>
+        <v>76.8</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>66.7</v>
       </c>
       <c r="E20" t="n">
-        <v>4.5</v>
+        <v>13.6</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>44.4</v>
       </c>
       <c r="G20" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="H20" t="n">
-        <v>38.5</v>
+        <v>47.7</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>59.4</v>
+        <v>57.5</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2</v>
+        <v>5.1</v>
       </c>
       <c r="F21" t="n">
-        <v>42.1</v>
+        <v>27.3</v>
       </c>
       <c r="G21" t="n">
-        <v>11.4</v>
+        <v>15</v>
       </c>
       <c r="H21" t="n">
-        <v>45.5</v>
+        <v>54.5</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>21.1</v>
       </c>
       <c r="K21" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>28.6</v>
+        <v>18.2</v>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>45.5</v>
+        <v>22.2</v>
       </c>
       <c r="K22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="D23" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H23" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-16.7</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>33.3</v>
+        <v>51.4</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>59.4</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="H24" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>57.9</v>
+        <v>80</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
-        <v>9.3</v>
+        <v>28.6</v>
       </c>
       <c r="F25" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>23.3</v>
+        <v>45.5</v>
       </c>
       <c r="K25" t="n">
-        <v>-11.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>62.8</v>
+        <v>66.7</v>
       </c>
       <c r="D26" t="n">
-        <v>57.5</v>
+        <v>57.1</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>9.3</v>
+        <v>16.7</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>40</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>21.7</v>
+        <v>14.3</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D27" t="n">
         <v>50</v>
@@ -4469,12 +4958,14 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -4488,591 +4979,925 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C28" t="n">
-        <v>28.6</v>
+        <v>57.9</v>
       </c>
       <c r="D28" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>9.5</v>
+        <v>9.3</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G28" t="n">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
       <c r="H28" t="n">
         <v>50</v>
       </c>
       <c r="I28" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-28.6</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C29" t="n">
-        <v>71.4</v>
+        <v>62.8</v>
       </c>
       <c r="D29" t="n">
-        <v>70.2</v>
+        <v>57.5</v>
       </c>
       <c r="E29" t="n">
-        <v>23.5</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
-        <v>34.8</v>
+        <v>21.7</v>
       </c>
       <c r="K29" t="n">
-        <v>28.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C30" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
-      </c>
-      <c r="F30" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F30"/>
       <c r="G30" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31"/>
+        <v>9.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H31" t="n">
         <v>50</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C32" t="n">
-        <v>63</v>
+        <v>71.4</v>
       </c>
       <c r="D32" t="n">
-        <v>57.8</v>
+        <v>70.2</v>
       </c>
       <c r="E32" t="n">
-        <v>13.6</v>
+        <v>23.5</v>
       </c>
       <c r="F32" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="G32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>23.5</v>
+        <v>34.8</v>
       </c>
       <c r="K32" t="n">
-        <v>7.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C33" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D33" t="n">
-        <v>87.5</v>
+        <v>66.7</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H33" t="n">
-        <v>66.7</v>
+        <v>18.2</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C34" t="n">
-        <v>69.2</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>74.7</v>
+        <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="F34" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34"/>
       <c r="G34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C35" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="D35" t="n">
-        <v>63.2</v>
+        <v>57.8</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>13.6</v>
       </c>
       <c r="F35" t="n">
-        <v>30.8</v>
+        <v>41.7</v>
       </c>
       <c r="G35" t="n">
-        <v>15.4</v>
+        <v>11.5</v>
       </c>
       <c r="H35" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>21.4</v>
+        <v>23.5</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C36" t="n">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="D36" t="n">
-        <v>65.3</v>
+        <v>87.5</v>
       </c>
       <c r="E36" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>69.2</v>
       </c>
       <c r="D37" t="n">
-        <v>41.2</v>
+        <v>74.7</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G37" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="H37" t="n">
-        <v>33.3</v>
+        <v>57.9</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-20</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C38" t="n">
-        <v>14.3</v>
+        <v>61.5</v>
       </c>
       <c r="D38" t="n">
-        <v>44.1</v>
+        <v>63.2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F38" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="G38" t="n">
-        <v>28.6</v>
+        <v>15.4</v>
       </c>
       <c r="H38" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>33.3</v>
+        <v>21.4</v>
       </c>
       <c r="K38" t="n">
-        <v>-14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="D39" t="n">
-        <v>57.9</v>
+        <v>65.3</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G39" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-25</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C40" t="n">
-        <v>58.1</v>
+        <v>40</v>
       </c>
       <c r="D40" t="n">
-        <v>60.9</v>
+        <v>41.2</v>
       </c>
       <c r="E40" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>46.7</v>
+        <v>33.3</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="K40" t="n">
-        <v>16.6</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>44.1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41"/>
+      <c r="F41" t="n">
+        <v>33.3</v>
+      </c>
       <c r="G41" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K41" t="n">
-        <v>-66.7</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C42" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>63.4</v>
+        <v>38.9</v>
       </c>
       <c r="E42" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H42" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>27.8</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C43" t="n">
+        <v>50</v>
+      </c>
+      <c r="D43" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>25</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="n">
+        <v>50</v>
+      </c>
+      <c r="D44" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-16.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F46" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" t="n">
+        <v>50</v>
+      </c>
+      <c r="D47" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15</v>
+      </c>
+      <c r="F47" t="n">
         <v>40</v>
       </c>
-      <c r="D43" t="n">
+      <c r="G47" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>40</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" t="n">
+        <v>50</v>
+      </c>
+      <c r="D48" t="n">
+        <v>60</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H48" t="n">
+        <v>40</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" t="n">
+        <v>100</v>
+      </c>
+      <c r="D49" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" t="n">
+        <v>25</v>
+      </c>
+      <c r="J49" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50"/>
+      <c r="G50" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-66.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>50</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K51" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>80</v>
+      </c>
+      <c r="E52" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>50</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" t="n">
+        <v>40</v>
+      </c>
+      <c r="D53" t="n">
         <v>31.6</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E53" t="n">
         <v>7.1</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F53" t="n">
         <v>100</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G53" t="n">
         <v>40</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>33.3</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K53" t="n">
         <v>-20</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44"/>
-      <c r="B44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="D44" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F44" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="G44" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J44" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-3.2</v>
+    <row r="54">
+      <c r="A54"/>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" t="n">
+        <v>56</v>
+      </c>
+      <c r="D54" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-3.7</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -282,6 +282,9 @@
     <t xml:space="preserve">Brendan Boys</t>
   </si>
   <si>
+    <t xml:space="preserve">Callum Barton</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cameron Bendo</t>
   </si>
   <si>
@@ -297,27 +300,45 @@
     <t xml:space="preserve">Gabriel Lopez</t>
   </si>
   <si>
+    <t xml:space="preserve">Gannon Djekic</t>
+  </si>
+  <si>
     <t xml:space="preserve">Griffen Duenkler</t>
   </si>
   <si>
     <t xml:space="preserve">Jack Larmer</t>
   </si>
   <si>
+    <t xml:space="preserve">Jack Marcotte</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jack Symington</t>
   </si>
   <si>
+    <t xml:space="preserve">Jake Colombe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jared Wellman</t>
   </si>
   <si>
+    <t xml:space="preserve">Keaton Ruttle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lucas Bateman</t>
   </si>
   <si>
+    <t xml:space="preserve">Matteo Tedesco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matthew Kong</t>
   </si>
   <si>
     <t xml:space="preserve">Nolan Goranson</t>
   </si>
   <si>
+    <t xml:space="preserve">Parker Starkiss</t>
+  </si>
+  <si>
     <t xml:space="preserve">Patrick Vieira</t>
   </si>
   <si>
@@ -327,6 +348,15 @@
     <t xml:space="preserve">Preston Vieira</t>
   </si>
   <si>
+    <t xml:space="preserve">Recker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Vavoulas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tennyson Seguin</t>
+  </si>
+  <si>
     <t xml:space="preserve">League Average:</t>
   </si>
   <si>
@@ -474,6 +504,9 @@
     <t xml:space="preserve">Jordan Miller</t>
   </si>
   <si>
+    <t xml:space="preserve">Kurtis Joseph</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kyle Tamaki</t>
   </si>
   <si>
@@ -481,6 +514,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mattheo Tsebelis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Dufour</t>
   </si>
   <si>
     <t xml:space="preserve">Nathan Mazer</t>
@@ -538,8 +574,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K91" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K101" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K101"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -558,8 +594,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K54" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K56" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K56"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -915,31 +951,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E2" t="n">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G2" t="n">
-        <v>19.4</v>
+        <v>17.9</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="I2" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="3">
@@ -950,31 +986,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>76.7</v>
+        <v>77</v>
       </c>
       <c r="D3" t="n">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
       <c r="E3" t="n">
-        <v>61.6</v>
+        <v>62.9</v>
       </c>
       <c r="F3" t="n">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
       <c r="G3" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="J3" t="n">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="K3" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="4">
@@ -1117,31 +1153,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>79.6</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>23.1</v>
+        <v>22.1</v>
       </c>
       <c r="E8" t="n">
-        <v>56.5</v>
+        <v>57.9</v>
       </c>
       <c r="F8" t="n">
-        <v>23.1</v>
+        <v>22.1</v>
       </c>
       <c r="G8" t="n">
-        <v>26.1</v>
+        <v>24.8</v>
       </c>
       <c r="H8" t="n">
-        <v>8.9</v>
+        <v>8.3</v>
       </c>
       <c r="I8" t="n">
         <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>26.3</v>
+        <v>28.6</v>
       </c>
       <c r="K8" t="n">
-        <v>36.8</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="9">
@@ -1152,31 +1188,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>75.9</v>
+        <v>76.2</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>70.9</v>
+        <v>72.2</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>23.9</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>8.8</v>
       </c>
       <c r="I9" t="n">
-        <v>40.9</v>
+        <v>45.8</v>
       </c>
       <c r="J9" t="n">
-        <v>31.8</v>
+        <v>29.2</v>
       </c>
       <c r="K9" t="n">
-        <v>54.5</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="10">
@@ -1219,28 +1255,28 @@
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="E11" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="F11" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="G11" t="n">
-        <v>33.7</v>
+        <v>32</v>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>16.9</v>
       </c>
       <c r="I11" t="n">
-        <v>45.5</v>
+        <v>47.2</v>
       </c>
       <c r="J11" t="n">
-        <v>21.2</v>
+        <v>22.2</v>
       </c>
       <c r="K11" t="n">
-        <v>27.3</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="12">
@@ -1268,31 +1304,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>76.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="n">
-        <v>67.9</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>7.1</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>17.6</v>
       </c>
       <c r="H13" t="n">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="I13" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="J13" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K13" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="14">
@@ -1303,31 +1339,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57.9</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>9.5</v>
+        <v>8.7</v>
       </c>
       <c r="E14" t="n">
-        <v>48.4</v>
+        <v>54.3</v>
       </c>
       <c r="F14" t="n">
-        <v>9.5</v>
+        <v>8.7</v>
       </c>
       <c r="G14" t="n">
-        <v>23.1</v>
+        <v>21.1</v>
       </c>
       <c r="H14" t="n">
-        <v>22.2</v>
+        <v>15.4</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="J14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K14" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
@@ -1373,31 +1409,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>80.8</v>
+        <v>73.5</v>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="E16" t="n">
-        <v>69.7</v>
+        <v>62.8</v>
       </c>
       <c r="F16" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="G16" t="n">
-        <v>26.1</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="K16" t="n">
-        <v>22.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="17">
@@ -1408,31 +1444,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="E17" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="F17" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="G17" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>31.8</v>
+        <v>32.6</v>
       </c>
       <c r="K17" t="n">
-        <v>37.2</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="18">
@@ -3424,32 +3460,24 @@
         <v>86</v>
       </c>
       <c r="C75" t="n">
-        <v>91.7</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>50</v>
-      </c>
-      <c r="G75" t="n">
-        <v>21.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G75"/>
       <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I75" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J75" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="K75" t="n">
-        <v>71.4</v>
-      </c>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
@@ -3459,31 +3487,31 @@
         <v>86</v>
       </c>
       <c r="C76" t="n">
-        <v>60</v>
+        <v>91.7</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E76" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="77">
@@ -3494,25 +3522,25 @@
         <v>86</v>
       </c>
       <c r="C77" t="n">
+        <v>60</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>60</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
         <v>100</v>
-      </c>
-      <c r="D77" t="n">
-        <v>20</v>
-      </c>
-      <c r="E77" t="n">
-        <v>80</v>
-      </c>
-      <c r="F77" t="n">
-        <v>20</v>
-      </c>
-      <c r="G77" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>66.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3529,31 +3557,31 @@
         <v>86</v>
       </c>
       <c r="C78" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D78" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="E78" t="n">
+        <v>80</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
         <v>66.7</v>
       </c>
-      <c r="F78" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>50</v>
-      </c>
       <c r="J78" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3564,16 +3592,16 @@
         <v>86</v>
       </c>
       <c r="C79" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E79" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3582,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J79" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="80">
@@ -3599,31 +3627,31 @@
         <v>86</v>
       </c>
       <c r="C80" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D80" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>54.7</v>
+        <v>100</v>
       </c>
       <c r="F80" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K80" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -3634,31 +3662,31 @@
         <v>86</v>
       </c>
       <c r="C81" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="n">
-        <v>57.1</v>
+        <v>45.8</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G81" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H81" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J81" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3669,31 +3697,31 @@
         <v>86</v>
       </c>
       <c r="C82" t="n">
-        <v>70</v>
+        <v>83.3</v>
       </c>
       <c r="D82" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="E82" t="n">
-        <v>32.5</v>
+        <v>54.7</v>
       </c>
       <c r="F82" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="G82" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="J82" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="83">
@@ -3704,130 +3732,130 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="D83" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>53.6</v>
+        <v>57.1</v>
       </c>
       <c r="F83" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>46.7</v>
+        <v>25</v>
       </c>
       <c r="H83" t="n">
         <v>14.3</v>
       </c>
       <c r="I83" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K83" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
         <v>86</v>
       </c>
       <c r="C84" t="n">
-        <v>84.6</v>
+        <v>33.3</v>
       </c>
       <c r="D84" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="E84" t="n">
-        <v>70.3</v>
+        <v>11.1</v>
       </c>
       <c r="F84" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="G84" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I84" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>18.8</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B85" t="s">
         <v>86</v>
       </c>
       <c r="C85" t="n">
-        <v>68.6</v>
+        <v>70</v>
       </c>
       <c r="D85" t="n">
-        <v>9.1</v>
+        <v>37.5</v>
       </c>
       <c r="E85" t="n">
-        <v>59.5</v>
+        <v>32.5</v>
       </c>
       <c r="F85" t="n">
-        <v>9.1</v>
+        <v>37.5</v>
       </c>
       <c r="G85" t="n">
-        <v>23.1</v>
+        <v>17.6</v>
       </c>
       <c r="H85" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="J85" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="K85" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B86" t="s">
         <v>86</v>
       </c>
       <c r="C86" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E86" t="n">
-        <v>50</v>
+        <v>17.8</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I86" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3838,72 +3866,72 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B87" t="s">
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="D87" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="E87" t="n">
-        <v>70.9</v>
+        <v>53.6</v>
       </c>
       <c r="F87" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G87" t="n">
-        <v>27.3</v>
+        <v>46.7</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I87" t="n">
         <v>66.7</v>
       </c>
       <c r="J87" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="B88" t="s">
         <v>86</v>
       </c>
       <c r="C88" t="n">
-        <v>60</v>
+        <v>84.6</v>
       </c>
       <c r="D88" t="n">
-        <v>42.9</v>
+        <v>14.3</v>
       </c>
       <c r="E88" t="n">
-        <v>17.1</v>
+        <v>70.3</v>
       </c>
       <c r="F88" t="n">
-        <v>42.9</v>
+        <v>14.3</v>
       </c>
       <c r="G88" t="n">
-        <v>33.3</v>
+        <v>13</v>
       </c>
       <c r="H88" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="J88" t="n">
-        <v>100</v>
+        <v>18.8</v>
       </c>
       <c r="K88" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="89">
@@ -3914,28 +3942,28 @@
         <v>86</v>
       </c>
       <c r="C89" t="n">
-        <v>90</v>
+        <v>72.7</v>
       </c>
       <c r="D89" t="n">
         <v>16.7</v>
       </c>
       <c r="E89" t="n">
-        <v>73.3</v>
+        <v>56</v>
       </c>
       <c r="F89" t="n">
         <v>16.7</v>
       </c>
       <c r="G89" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J89" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3949,64 +3977,408 @@
         <v>86</v>
       </c>
       <c r="C90" t="n">
-        <v>100</v>
+        <v>68.6</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E90" t="n">
-        <v>100</v>
+        <v>59.5</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I90" t="n">
         <v>33.3</v>
       </c>
       <c r="J90" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K90" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>104</v>
+      </c>
+      <c r="B91" t="s">
+        <v>86</v>
+      </c>
+      <c r="C91" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>20</v>
+      </c>
+      <c r="I91" t="n">
+        <v>50</v>
+      </c>
+      <c r="J91" t="n">
+        <v>50</v>
+      </c>
+      <c r="K91" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>105</v>
+      </c>
+      <c r="B92" t="s">
+        <v>86</v>
+      </c>
+      <c r="C92" t="n">
+        <v>50</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>50</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>106</v>
+      </c>
+      <c r="B93" t="s">
+        <v>86</v>
+      </c>
+      <c r="C93" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D93" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>20</v>
+      </c>
+      <c r="G93" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J93" t="n">
         <v>33.3</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K93" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>107</v>
+      </c>
+      <c r="B94" t="s">
+        <v>86</v>
+      </c>
+      <c r="C94" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="D94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E94" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>100</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B95" t="s">
+        <v>86</v>
+      </c>
+      <c r="C95" t="n">
+        <v>60</v>
+      </c>
+      <c r="D95" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E95" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G95" t="n">
         <v>33.3</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91"/>
-      <c r="B91" t="s">
-        <v>104</v>
-      </c>
-      <c r="C91" t="n">
-        <v>70.1</v>
-      </c>
-      <c r="D91" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="E91" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="F91" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="G91" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H91" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I91" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="J91" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="K91" t="n">
-        <v>31</v>
+      <c r="H95" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>100</v>
+      </c>
+      <c r="K95" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>109</v>
+      </c>
+      <c r="B96" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" t="n">
+        <v>90</v>
+      </c>
+      <c r="D96" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E96" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G96" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>50</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>110</v>
+      </c>
+      <c r="B97" t="s">
+        <v>86</v>
+      </c>
+      <c r="C97" t="n">
+        <v>100</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>100</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K97" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>111</v>
+      </c>
+      <c r="B98" t="s">
+        <v>86</v>
+      </c>
+      <c r="C98" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>50</v>
+      </c>
+      <c r="H98" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I98"/>
+      <c r="J98"/>
+      <c r="K98"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>112</v>
+      </c>
+      <c r="B99" t="s">
+        <v>86</v>
+      </c>
+      <c r="C99" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D99" t="n">
+        <v>20</v>
+      </c>
+      <c r="E99" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F99" t="n">
+        <v>20</v>
+      </c>
+      <c r="G99" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>50</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>113</v>
+      </c>
+      <c r="B100" t="s">
+        <v>86</v>
+      </c>
+      <c r="C100" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>20</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>100</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101"/>
+      <c r="B101" t="s">
+        <v>114</v>
+      </c>
+      <c r="C101" t="n">
+        <v>67.6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="F101" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>50</v>
+      </c>
+      <c r="J101" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K101" t="n">
+        <v>29.6</v>
       </c>
     </row>
   </sheetData>
@@ -4038,22 +4410,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -4062,13 +4434,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2">
@@ -4143,42 +4515,42 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>58.1</v>
+        <v>57.4</v>
       </c>
       <c r="D4" t="n">
-        <v>66.8</v>
+        <v>66.5</v>
       </c>
       <c r="E4" t="n">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="F4" t="n">
         <v>36.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -4213,7 +4585,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -4248,7 +4620,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -4283,7 +4655,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -4353,7 +4725,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -4388,42 +4760,42 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>59.1</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>55.9</v>
+        <v>56.6</v>
       </c>
       <c r="E11" t="n">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
       <c r="F11" t="n">
-        <v>34.6</v>
+        <v>38.2</v>
       </c>
       <c r="G11" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>51.2</v>
+        <v>52.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>20.9</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -4456,7 +4828,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -4491,7 +4863,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -4526,7 +4898,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -4561,7 +4933,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -4594,42 +4966,42 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>66.1</v>
       </c>
       <c r="D17" t="n">
-        <v>64.9</v>
+        <v>63.3</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>19.2</v>
       </c>
       <c r="F17" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
       <c r="G17" t="n">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="H17" t="n">
-        <v>52.2</v>
+        <v>53.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>20.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -4664,7 +5036,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -4699,7 +5071,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -4734,7 +5106,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -4769,7 +5141,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -4804,7 +5176,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -4839,7 +5211,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -4874,7 +5246,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -4909,7 +5281,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -4944,7 +5316,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
@@ -4979,7 +5351,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -5014,7 +5386,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -5049,7 +5421,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -5082,7 +5454,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
@@ -5117,7 +5489,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -5152,7 +5524,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -5187,7 +5559,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -5220,7 +5592,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
         <v>62</v>
@@ -5255,7 +5627,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B36" t="s">
         <v>62</v>
@@ -5290,7 +5662,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
         <v>62</v>
@@ -5325,7 +5697,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
@@ -5360,7 +5732,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B39" t="s">
         <v>75</v>
@@ -5395,7 +5767,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B40" t="s">
         <v>86</v>
@@ -5430,7 +5802,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B41" t="s">
         <v>86</v>
@@ -5465,7 +5837,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B42" t="s">
         <v>86</v>
@@ -5500,7 +5872,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
         <v>86</v>
@@ -5535,7 +5907,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
         <v>86</v>
@@ -5570,7 +5942,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
         <v>86</v>
@@ -5591,7 +5963,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s">
         <v>86</v>
@@ -5626,7 +5998,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B47" t="s">
         <v>86</v>
@@ -5661,7 +6033,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
         <v>86</v>
@@ -5696,7 +6068,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
         <v>86</v>
@@ -5731,173 +6103,243 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B50" t="s">
         <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>53.3</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50"/>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
       <c r="G50" t="n">
-        <v>66.7</v>
+        <v>11.1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="K50" t="n">
-        <v>-66.7</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B51" t="s">
         <v>86</v>
       </c>
       <c r="C51" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>63.4</v>
+        <v>20</v>
       </c>
       <c r="E51" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F51" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F51"/>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H51" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>27.8</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B52" t="s">
         <v>86</v>
       </c>
       <c r="C52" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D52" t="n">
-        <v>80</v>
+        <v>63.4</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B53" t="s">
         <v>86</v>
       </c>
       <c r="C53" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D53" t="n">
+        <v>80</v>
+      </c>
+      <c r="E53" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>50</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" t="n">
+        <v>52</v>
+      </c>
+      <c r="D54" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" t="n">
         <v>40</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D55" t="n">
         <v>31.6</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>7.1</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F55" t="n">
         <v>100</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G55" t="n">
         <v>40</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
         <v>33.3</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K55" t="n">
         <v>-20</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54"/>
-      <c r="B54" t="s">
-        <v>104</v>
-      </c>
-      <c r="C54" t="n">
-        <v>56</v>
-      </c>
-      <c r="D54" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="E54" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F54" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="G54" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J54" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="K54" t="n">
-        <v>-3.7</v>
+    <row r="56">
+      <c r="A56"/>
+      <c r="B56" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G56" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-3.8</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -282,72 +282,75 @@
     <t xml:space="preserve">Brendan Boys</t>
   </si>
   <si>
+    <t xml:space="preserve">Cameron Bendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cole Geldart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Leonard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davis Llewellyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffen Duenkler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Larmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Symington</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jared Wellman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Bateman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Kong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Goranson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Vieira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Dineen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preston Vieira</t>
+  </si>
+  <si>
     <t xml:space="preserve">Callum Barton</t>
   </si>
   <si>
-    <t xml:space="preserve">Cameron Bendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cole Geldart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Leonard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davis Llewellyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Lopez</t>
+    <t xml:space="preserve">Windsor Lancers</t>
   </si>
   <si>
     <t xml:space="preserve">Gannon Djekic</t>
   </si>
   <si>
-    <t xml:space="preserve">Griffen Duenkler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Larmer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jack Marcotte</t>
   </si>
   <si>
-    <t xml:space="preserve">Jack Symington</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jake Colombe</t>
   </si>
   <si>
-    <t xml:space="preserve">Jared Wellman</t>
-  </si>
-  <si>
     <t xml:space="preserve">Keaton Ruttle</t>
   </si>
   <si>
-    <t xml:space="preserve">Lucas Bateman</t>
-  </si>
-  <si>
     <t xml:space="preserve">Matteo Tedesco</t>
   </si>
   <si>
-    <t xml:space="preserve">Matthew Kong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Goranson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parker Starkiss</t>
   </si>
   <si>
-    <t xml:space="preserve">Patrick Vieira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Dineen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preston Vieira</t>
-  </si>
-  <si>
     <t xml:space="preserve">Recker</t>
   </si>
   <si>
@@ -504,22 +507,22 @@
     <t xml:space="preserve">Jordan Miller</t>
   </si>
   <si>
+    <t xml:space="preserve">Kyle Tamaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Conlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattheo Tsebelis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Mazer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kurtis Joseph</t>
   </si>
   <si>
-    <t xml:space="preserve">Kyle Tamaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Conlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattheo Tsebelis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nathan Dufour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Mazer</t>
   </si>
 </sst>
 </file>
@@ -3460,24 +3463,32 @@
         <v>86</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75"/>
+        <v>50</v>
+      </c>
+      <c r="G75" t="n">
+        <v>21.4</v>
+      </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I75"/>
-      <c r="J75"/>
-      <c r="K75"/>
+      <c r="I75" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>71.4</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
@@ -3487,31 +3498,31 @@
         <v>86</v>
       </c>
       <c r="C76" t="n">
-        <v>91.7</v>
+        <v>60</v>
       </c>
       <c r="D76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>41.7</v>
+        <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3522,25 +3533,25 @@
         <v>86</v>
       </c>
       <c r="C77" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E77" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3557,31 +3568,31 @@
         <v>86</v>
       </c>
       <c r="C78" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>8.3</v>
       </c>
       <c r="E78" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>8.3</v>
       </c>
       <c r="G78" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="79">
@@ -3592,16 +3603,16 @@
         <v>86</v>
       </c>
       <c r="C79" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D79" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3610,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="K79" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3627,31 +3638,31 @@
         <v>86</v>
       </c>
       <c r="C80" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E80" t="n">
-        <v>100</v>
+        <v>54.7</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J80" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="81">
@@ -3662,31 +3673,31 @@
         <v>86</v>
       </c>
       <c r="C81" t="n">
-        <v>58.3</v>
+        <v>57.1</v>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>45.8</v>
+        <v>57.1</v>
       </c>
       <c r="F81" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I81" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82">
@@ -3697,31 +3708,31 @@
         <v>86</v>
       </c>
       <c r="C82" t="n">
-        <v>83.3</v>
+        <v>70</v>
       </c>
       <c r="D82" t="n">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
       <c r="E82" t="n">
-        <v>54.7</v>
+        <v>32.5</v>
       </c>
       <c r="F82" t="n">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
       <c r="G82" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="J82" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K82" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -3732,130 +3743,130 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="E83" t="n">
-        <v>57.1</v>
+        <v>53.6</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="G83" t="n">
-        <v>25</v>
+        <v>46.7</v>
       </c>
       <c r="H83" t="n">
         <v>14.3</v>
       </c>
       <c r="I83" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J83" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="B84" t="s">
         <v>86</v>
       </c>
       <c r="C84" t="n">
-        <v>33.3</v>
+        <v>84.6</v>
       </c>
       <c r="D84" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="E84" t="n">
-        <v>11.1</v>
+        <v>70.3</v>
       </c>
       <c r="F84" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="G84" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="J84" t="n">
-        <v>50</v>
+        <v>18.8</v>
       </c>
       <c r="K84" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B85" t="s">
         <v>86</v>
       </c>
       <c r="C85" t="n">
-        <v>70</v>
+        <v>68.6</v>
       </c>
       <c r="D85" t="n">
-        <v>37.5</v>
+        <v>9.1</v>
       </c>
       <c r="E85" t="n">
-        <v>32.5</v>
+        <v>59.5</v>
       </c>
       <c r="F85" t="n">
-        <v>37.5</v>
+        <v>9.1</v>
       </c>
       <c r="G85" t="n">
-        <v>17.6</v>
+        <v>23.1</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I85" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="J85" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K85" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B86" t="s">
         <v>86</v>
       </c>
       <c r="C86" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D86" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>17.8</v>
+        <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3866,72 +3877,72 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B87" t="s">
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="D87" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="E87" t="n">
-        <v>53.6</v>
+        <v>70.9</v>
       </c>
       <c r="F87" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="G87" t="n">
-        <v>46.7</v>
+        <v>27.3</v>
       </c>
       <c r="H87" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>66.7</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K87" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="B88" t="s">
         <v>86</v>
       </c>
       <c r="C88" t="n">
-        <v>84.6</v>
+        <v>60</v>
       </c>
       <c r="D88" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="E88" t="n">
-        <v>70.3</v>
+        <v>17.1</v>
       </c>
       <c r="F88" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="G88" t="n">
-        <v>13</v>
+        <v>33.3</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I88" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>18.8</v>
+        <v>100</v>
       </c>
       <c r="K88" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -3942,28 +3953,28 @@
         <v>86</v>
       </c>
       <c r="C89" t="n">
-        <v>72.7</v>
+        <v>90</v>
       </c>
       <c r="D89" t="n">
         <v>16.7</v>
       </c>
       <c r="E89" t="n">
-        <v>56</v>
+        <v>73.3</v>
       </c>
       <c r="F89" t="n">
         <v>16.7</v>
       </c>
       <c r="G89" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>33.3</v>
       </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>100</v>
-      </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3977,31 +3988,31 @@
         <v>86</v>
       </c>
       <c r="C90" t="n">
-        <v>68.6</v>
+        <v>100</v>
       </c>
       <c r="D90" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="F90" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
         <v>33.3</v>
       </c>
       <c r="J90" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="K90" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="91">
@@ -4009,63 +4020,55 @@
         <v>104</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C91" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
+      <c r="G91"/>
       <c r="H91" t="n">
-        <v>20</v>
-      </c>
-      <c r="I91" t="n">
-        <v>50</v>
-      </c>
-      <c r="J91" t="n">
-        <v>50</v>
-      </c>
-      <c r="K91" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>106</v>
+      </c>
+      <c r="B92" t="s">
         <v>105</v>
       </c>
-      <c r="B92" t="s">
-        <v>86</v>
-      </c>
       <c r="C92" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="n">
-        <v>50</v>
+        <v>45.8</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -4076,34 +4079,34 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C93" t="n">
-        <v>90.9</v>
+        <v>33.3</v>
       </c>
       <c r="D93" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E93" t="n">
-        <v>70.9</v>
+        <v>11.1</v>
       </c>
       <c r="F93" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="G93" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I93" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K93" t="n">
         <v>50</v>
@@ -4111,28 +4114,28 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C94" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>22.2</v>
       </c>
       <c r="E94" t="n">
-        <v>29.2</v>
+        <v>17.8</v>
       </c>
       <c r="F94" t="n">
-        <v>12.5</v>
+        <v>22.2</v>
       </c>
       <c r="G94" t="n">
-        <v>16.7</v>
+        <v>75</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I94" t="n">
         <v>100</v>
@@ -4146,115 +4149,115 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C95" t="n">
-        <v>60</v>
+        <v>72.7</v>
       </c>
       <c r="D95" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="E95" t="n">
-        <v>17.1</v>
+        <v>56</v>
       </c>
       <c r="F95" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="G95" t="n">
         <v>33.3</v>
       </c>
       <c r="H95" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J95" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C96" t="n">
-        <v>90</v>
+        <v>57.1</v>
       </c>
       <c r="D96" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>73.3</v>
+        <v>57.1</v>
       </c>
       <c r="F96" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I96" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J96" t="n">
         <v>50</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C97" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="D97" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E97" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F97" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G97" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
         <v>100</v>
       </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>100</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>33.3</v>
-      </c>
       <c r="J97" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C98" t="n">
         <v>16.7</v>
@@ -4280,10 +4283,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C99" t="n">
         <v>71.4</v>
@@ -4315,10 +4318,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C100" t="n">
         <v>66.7</v>
@@ -4351,7 +4354,7 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C101" t="n">
         <v>67.6</v>
@@ -4410,22 +4413,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -4434,13 +4437,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2">
@@ -4515,7 +4518,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -4550,7 +4553,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -4585,7 +4588,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -4620,7 +4623,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -4655,7 +4658,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -4725,7 +4728,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -4760,7 +4763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -4795,7 +4798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -4828,7 +4831,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -4863,7 +4866,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -4898,7 +4901,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -4933,7 +4936,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -4966,7 +4969,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -5001,7 +5004,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -5036,7 +5039,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -5071,7 +5074,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -5106,7 +5109,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -5141,7 +5144,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -5176,7 +5179,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -5211,7 +5214,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -5281,7 +5284,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -5316,7 +5319,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
@@ -5351,7 +5354,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -5386,7 +5389,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -5421,7 +5424,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -5454,7 +5457,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
@@ -5489,7 +5492,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -5524,7 +5527,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -5559,7 +5562,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -5592,7 +5595,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
         <v>62</v>
@@ -5627,7 +5630,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
         <v>62</v>
@@ -5662,7 +5665,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
         <v>62</v>
@@ -5697,7 +5700,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
@@ -5732,7 +5735,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B39" t="s">
         <v>75</v>
@@ -5767,7 +5770,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B40" t="s">
         <v>86</v>
@@ -5802,7 +5805,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" t="s">
         <v>86</v>
@@ -5837,7 +5840,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
         <v>86</v>
@@ -5872,7 +5875,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" t="s">
         <v>86</v>
@@ -5907,7 +5910,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
         <v>86</v>
@@ -5942,7 +5945,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
         <v>86</v>
@@ -5963,7 +5966,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
         <v>86</v>
@@ -5998,7 +6001,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B47" t="s">
         <v>86</v>
@@ -6033,7 +6036,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s">
         <v>86</v>
@@ -6068,7 +6071,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
         <v>86</v>
@@ -6103,216 +6106,216 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B50" t="s">
         <v>86</v>
       </c>
       <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50"/>
+      <c r="G50" t="n">
         <v>66.7</v>
       </c>
-      <c r="D50" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>11.1</v>
-      </c>
       <c r="H50" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.1</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B51" t="s">
         <v>86</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>63.4</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51"/>
+        <v>17.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>50</v>
+      </c>
       <c r="G51" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-66.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B52" t="s">
         <v>86</v>
       </c>
       <c r="C52" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="D52" t="n">
-        <v>63.4</v>
+        <v>80</v>
       </c>
       <c r="E52" t="n">
-        <v>17.6</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B53" t="s">
         <v>86</v>
       </c>
       <c r="C53" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D53" t="n">
-        <v>80</v>
+        <v>31.6</v>
       </c>
       <c r="E53" t="n">
-        <v>50</v>
+        <v>7.1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C54" t="n">
-        <v>52</v>
+        <v>66.7</v>
       </c>
       <c r="D54" t="n">
-        <v>55.2</v>
+        <v>53.3</v>
       </c>
       <c r="E54" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H54" t="n">
         <v>28.6</v>
       </c>
-      <c r="G54" t="n">
-        <v>8</v>
-      </c>
-      <c r="H54" t="n">
-        <v>47.4</v>
-      </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B55" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C55" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
-        <v>31.6</v>
+        <v>55.2</v>
       </c>
       <c r="E55" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="G55" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="K55" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C56" t="n">
         <v>56.1</v>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -78,9 +78,18 @@
     <t xml:space="preserve">Haydon Cupolo</t>
   </si>
   <si>
+    <t xml:space="preserve">Jack Cohen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Shannon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jaden Leeder</t>
   </si>
   <si>
+    <t xml:space="preserve">Jaxon Price</t>
+  </si>
+  <si>
     <t xml:space="preserve">Johnny Banks</t>
   </si>
   <si>
@@ -99,9 +108,15 @@
     <t xml:space="preserve">Nolan Phelan</t>
   </si>
   <si>
+    <t xml:space="preserve">Parker Starkiss</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reid Lunney</t>
   </si>
   <si>
+    <t xml:space="preserve">Tim Somerville</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tobey Drennan</t>
   </si>
   <si>
@@ -333,6 +348,9 @@
     <t xml:space="preserve">Windsor Lancers</t>
   </si>
   <si>
+    <t xml:space="preserve">Cullen Rooney</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gannon Djekic</t>
   </si>
   <si>
@@ -348,9 +366,6 @@
     <t xml:space="preserve">Matteo Tedesco</t>
   </si>
   <si>
-    <t xml:space="preserve">Parker Starkiss</t>
-  </si>
-  <si>
     <t xml:space="preserve">Recker</t>
   </si>
   <si>
@@ -396,15 +411,15 @@
     <t xml:space="preserve">Evan Marks</t>
   </si>
   <si>
-    <t xml:space="preserve">Jack Cohen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jack Tiessen</t>
   </si>
   <si>
     <t xml:space="preserve">Joel Palmer</t>
   </si>
   <si>
+    <t xml:space="preserve">Max Burroughsford</t>
+  </si>
+  <si>
     <t xml:space="preserve">Max Van Dam</t>
   </si>
   <si>
@@ -519,10 +534,19 @@
     <t xml:space="preserve">Nathan Mazer</t>
   </si>
   <si>
+    <t xml:space="preserve">Ethan Lawhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JJ Robinson-Evans</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kurtis Joseph</t>
   </si>
   <si>
     <t xml:space="preserve">Nathan Dufour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zachary Dunne</t>
   </si>
 </sst>
 </file>
@@ -577,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K101" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K107" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K107"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -597,8 +621,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K56" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K61" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K61"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -954,31 +978,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>60.4</v>
+        <v>61.1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="E2" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="G2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H2" t="n">
         <v>17.9</v>
       </c>
-      <c r="H2" t="n">
-        <v>18.9</v>
-      </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="K2" t="n">
-        <v>41.7</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="3">
@@ -1129,14 +1153,18 @@
         <v>12</v>
       </c>
       <c r="C7"/>
-      <c r="D7"/>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
       <c r="E7"/>
-      <c r="F7"/>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1156,31 +1184,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>79.2</v>
       </c>
       <c r="D8" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="E8" t="n">
-        <v>57.9</v>
+        <v>56.7</v>
       </c>
       <c r="F8" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="G8" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
       <c r="H8" t="n">
-        <v>8.3</v>
+        <v>9.4</v>
       </c>
       <c r="I8" t="n">
         <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>28.6</v>
+        <v>29.5</v>
       </c>
       <c r="K8" t="n">
-        <v>38.1</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="9">
@@ -1191,31 +1219,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>76.2</v>
+        <v>77.3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="E9" t="n">
-        <v>72.2</v>
+        <v>73.9</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>20.8</v>
       </c>
       <c r="H9" t="n">
-        <v>8.8</v>
+        <v>10.5</v>
       </c>
       <c r="I9" t="n">
-        <v>45.8</v>
+        <v>48</v>
       </c>
       <c r="J9" t="n">
-        <v>29.2</v>
+        <v>28</v>
       </c>
       <c r="K9" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -1255,31 +1283,31 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>16.9</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>47.2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>22.2</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1289,15 +1317,33 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
+      <c r="C12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -1307,31 +1353,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>76.5</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>17.7</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>49.3</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5</v>
+        <v>17.7</v>
       </c>
       <c r="G13" t="n">
-        <v>17.6</v>
+        <v>32</v>
       </c>
       <c r="H13" t="n">
-        <v>15.4</v>
+        <v>16.9</v>
       </c>
       <c r="I13" t="n">
-        <v>44.4</v>
+        <v>47.2</v>
       </c>
       <c r="J13" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="K13" t="n">
-        <v>66.7</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="14">
@@ -1342,31 +1388,25 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
-      </c>
-      <c r="D14" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="E14" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
       <c r="G14" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1376,33 +1416,15 @@
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="I15" t="n">
-        <v>35</v>
-      </c>
-      <c r="J15" t="n">
-        <v>40</v>
-      </c>
-      <c r="K15" t="n">
-        <v>47.4</v>
-      </c>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -1412,31 +1434,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>73.5</v>
+        <v>73.7</v>
       </c>
       <c r="D16" t="n">
-        <v>10.7</v>
+        <v>9.7</v>
       </c>
       <c r="E16" t="n">
-        <v>62.8</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>10.7</v>
+        <v>9.7</v>
       </c>
       <c r="G16" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I16" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="J16" t="n">
-        <v>23.1</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
-        <v>33.3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -1447,31 +1469,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>79.5</v>
+        <v>62.5</v>
       </c>
       <c r="D17" t="n">
-        <v>17.3</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="n">
-        <v>62.2</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>17.3</v>
+        <v>12.5</v>
       </c>
       <c r="G17" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7</v>
+        <v>12.5</v>
       </c>
       <c r="I17" t="n">
-        <v>39.1</v>
+        <v>36.4</v>
       </c>
       <c r="J17" t="n">
-        <v>32.6</v>
+        <v>45.5</v>
       </c>
       <c r="K17" t="n">
-        <v>35.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="18">
@@ -1482,31 +1504,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>55.4</v>
+        <v>78.6</v>
       </c>
       <c r="D18" t="n">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="E18" t="n">
-        <v>40.5</v>
+        <v>63.2</v>
       </c>
       <c r="F18" t="n">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="G18" t="n">
-        <v>11.8</v>
+        <v>30.8</v>
       </c>
       <c r="H18" t="n">
-        <v>13.5</v>
+        <v>11.4</v>
       </c>
       <c r="I18" t="n">
-        <v>51.5</v>
+        <v>41.7</v>
       </c>
       <c r="J18" t="n">
-        <v>21.2</v>
+        <v>37.5</v>
       </c>
       <c r="K18" t="n">
-        <v>27.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="19">
@@ -1517,28 +1539,28 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>80</v>
+        <v>73.5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>62.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>16.7</v>
+        <v>30.8</v>
       </c>
       <c r="J19" t="n">
-        <v>83.3</v>
+        <v>23.1</v>
       </c>
       <c r="K19" t="n">
         <v>33.3</v>
@@ -1549,124 +1571,124 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>79.4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>62.2</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>23.9</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E21" t="n">
         <v>16.7</v>
       </c>
-      <c r="E21" t="n">
-        <v>50</v>
-      </c>
       <c r="F21" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
       </c>
       <c r="H21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>86.7</v>
+        <v>55.4</v>
       </c>
       <c r="D22" t="n">
-        <v>9.1</v>
+        <v>14.9</v>
       </c>
       <c r="E22" t="n">
-        <v>77.6</v>
+        <v>40.5</v>
       </c>
       <c r="F22" t="n">
-        <v>9.1</v>
+        <v>14.9</v>
       </c>
       <c r="G22" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="H22" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="I22" t="n">
-        <v>62.5</v>
+        <v>51.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="K22" t="n">
-        <v>12.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1675,83 +1697,83 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>52.5</v>
+        <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="J24" t="n">
-        <v>54.5</v>
+        <v>83.3</v>
       </c>
       <c r="K24" t="n">
-        <v>9.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
       <c r="C25" t="n">
-        <v>82.1</v>
+        <v>100</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>62.1</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>21.4</v>
+        <v>50</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>53.8</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1759,34 +1781,34 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>76</v>
+        <v>66.7</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>16.7</v>
       </c>
       <c r="E26" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>16.7</v>
       </c>
       <c r="G26" t="n">
-        <v>31.8</v>
+        <v>50</v>
       </c>
       <c r="H26" t="n">
-        <v>14.3</v>
+        <v>30</v>
       </c>
       <c r="I26" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="J26" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>11.1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27">
@@ -1794,34 +1816,34 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C27" t="n">
-        <v>71.9</v>
+        <v>86.7</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>9.1</v>
       </c>
       <c r="E27" t="n">
-        <v>67.9</v>
+        <v>77.6</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>9.1</v>
       </c>
       <c r="G27" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="H27" t="n">
         <v>11.1</v>
       </c>
       <c r="I27" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28">
@@ -1829,34 +1851,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C28" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D28" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>78.4</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>26.7</v>
+        <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1864,34 +1886,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C29" t="n">
-        <v>59.3</v>
+        <v>62.5</v>
       </c>
       <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I29" t="n">
         <v>9.1</v>
       </c>
-      <c r="E29" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="J29" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K29" t="n">
         <v>9.1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>50</v>
-      </c>
-      <c r="K29" t="n">
-        <v>16.7</v>
       </c>
     </row>
     <row r="30">
@@ -1899,34 +1921,34 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>82.1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>62.1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="31">
@@ -1934,34 +1956,34 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>63.6</v>
+        <v>76</v>
       </c>
       <c r="D31" t="n">
-        <v>22.2</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>41.4</v>
+        <v>63</v>
       </c>
       <c r="F31" t="n">
-        <v>22.2</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K31" t="n">
         <v>11.1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>80</v>
-      </c>
-      <c r="J31" t="n">
-        <v>20</v>
-      </c>
-      <c r="K31" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -1969,34 +1991,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C32" t="n">
-        <v>48.6</v>
+        <v>71.9</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>40.6</v>
+        <v>67.9</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="H32" t="n">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="I32" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J32" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>22.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -2004,34 +2026,34 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>56.2</v>
+        <v>84</v>
       </c>
       <c r="D33" t="n">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="E33" t="n">
-        <v>26.2</v>
+        <v>78.4</v>
       </c>
       <c r="F33" t="n">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="G33" t="n">
-        <v>41.7</v>
+        <v>4.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I33" t="n">
-        <v>75</v>
+        <v>26.7</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="34">
@@ -2039,209 +2061,209 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>59.3</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G34" t="n">
-        <v>66.7</v>
+        <v>42.1</v>
       </c>
       <c r="H34" t="n">
-        <v>42.9</v>
+        <v>13.3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J34" t="n">
         <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C36" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>80</v>
+      </c>
+      <c r="J36" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" t="n">
         <v>40</v>
-      </c>
-      <c r="D36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E36" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G36" t="n">
-        <v>20</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>100</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>47.1</v>
+        <v>48.6</v>
       </c>
       <c r="D37" t="n">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>30.4</v>
+        <v>40.6</v>
       </c>
       <c r="F37" t="n">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I37" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="J37" t="n">
-        <v>28.6</v>
+        <v>22.2</v>
       </c>
       <c r="K37" t="n">
-        <v>57.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>66.7</v>
+        <v>56.2</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E38" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>30</v>
+      </c>
+      <c r="G38" t="n">
         <v>41.7</v>
       </c>
-      <c r="F38" t="n">
-        <v>25</v>
-      </c>
-      <c r="G38" t="n">
-        <v>25</v>
-      </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
         <v>51</v>
       </c>
-      <c r="B39" t="s">
-        <v>46</v>
-      </c>
       <c r="C39" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>67.5</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I39" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2249,61 +2271,69 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40"/>
+      <c r="G40" t="n">
+        <v>26.7</v>
+      </c>
       <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40"/>
-      <c r="J40"/>
-      <c r="K40"/>
+        <v>10</v>
+      </c>
+      <c r="I40" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K40" t="n">
+        <v>66.7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C41" t="n">
-        <v>57.7</v>
+        <v>40</v>
       </c>
       <c r="D41" t="n">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="n">
-        <v>40.1</v>
+        <v>27.5</v>
       </c>
       <c r="F41" t="n">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="G41" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2311,34 +2341,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>30.4</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K42" t="n">
-        <v>25</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="43">
@@ -2346,19 +2376,19 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D43" t="n">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="E43" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="F43" t="n">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="G43" t="n">
         <v>25</v>
@@ -2367,13 +2397,13 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -2381,34 +2411,34 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C44" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K44" t="n">
         <v>66.7</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>25</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>50</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -2416,69 +2446,61 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C45" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>41.3</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G45" t="n">
-        <v>38.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G45"/>
       <c r="H45" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>50</v>
-      </c>
-      <c r="J45" t="n">
-        <v>25</v>
-      </c>
-      <c r="K45" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C46" t="n">
-        <v>66.7</v>
+        <v>57.7</v>
       </c>
       <c r="D46" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="E46" t="n">
-        <v>50</v>
+        <v>40.1</v>
       </c>
       <c r="F46" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="G46" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
       <c r="H46" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>45.5</v>
       </c>
       <c r="J46" t="n">
-        <v>40</v>
+        <v>27.3</v>
       </c>
       <c r="K46" t="n">
-        <v>20</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="47">
@@ -2486,34 +2508,34 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>36.4</v>
+        <v>50</v>
       </c>
       <c r="D47" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>-33.6</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>45.5</v>
+        <v>20</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
@@ -2521,34 +2543,34 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="D48" t="n">
-        <v>38.5</v>
+        <v>7.7</v>
       </c>
       <c r="E48" t="n">
-        <v>24</v>
+        <v>42.3</v>
       </c>
       <c r="F48" t="n">
-        <v>38.5</v>
+        <v>7.7</v>
       </c>
       <c r="G48" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="49">
@@ -2556,25 +2578,25 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C49" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="D49" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8.3</v>
+        <v>66.7</v>
       </c>
       <c r="F49" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>25</v>
       </c>
       <c r="H49" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>50</v>
@@ -2588,28 +2610,34 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C50" t="n">
-        <v>100</v>
-      </c>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
+        <v>55.6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F50" t="n">
+        <v>14.3</v>
+      </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I50" t="n">
         <v>50</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K50" t="n">
         <v>50</v>
@@ -2617,142 +2645,142 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C51" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D51" t="n">
-        <v>36.4</v>
+        <v>16.7</v>
       </c>
       <c r="E51" t="n">
-        <v>42.2</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>36.4</v>
+        <v>16.7</v>
       </c>
       <c r="G51" t="n">
-        <v>13.3</v>
+        <v>33.3</v>
       </c>
       <c r="H51" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I51" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>76.9</v>
+        <v>36.4</v>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E52" t="n">
-        <v>51.9</v>
+        <v>-33.6</v>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="G52" t="n">
-        <v>9.1</v>
+        <v>45.5</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J52" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K52" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>83.3</v>
+        <v>62.5</v>
       </c>
       <c r="D53" t="n">
-        <v>28.6</v>
+        <v>38.5</v>
       </c>
       <c r="E53" t="n">
-        <v>54.7</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
-        <v>28.6</v>
+        <v>38.5</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H53" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J53" t="n">
         <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" t="s">
         <v>67</v>
       </c>
-      <c r="B54" t="s">
-        <v>62</v>
-      </c>
       <c r="C54" t="n">
-        <v>57.1</v>
+        <v>53.8</v>
       </c>
       <c r="D54" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G54" t="n">
         <v>25</v>
       </c>
-      <c r="E54" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>25</v>
-      </c>
-      <c r="G54" t="n">
-        <v>40</v>
-      </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I54" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
@@ -2760,34 +2788,28 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C55" t="n">
         <v>100</v>
       </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>100</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
       <c r="G55" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -2795,34 +2817,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C56" t="n">
-        <v>60</v>
+        <v>78.6</v>
       </c>
       <c r="D56" t="n">
-        <v>16.7</v>
+        <v>36.4</v>
       </c>
       <c r="E56" t="n">
-        <v>43.3</v>
+        <v>42.2</v>
       </c>
       <c r="F56" t="n">
-        <v>16.7</v>
+        <v>36.4</v>
       </c>
       <c r="G56" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="H56" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="I56" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J56" t="n">
         <v>50</v>
       </c>
       <c r="K56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2830,34 +2852,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C57" t="n">
-        <v>58.8</v>
+        <v>76.9</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E57" t="n">
-        <v>58.8</v>
+        <v>51.9</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G57" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="H57" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J57" t="n">
-        <v>16.7</v>
+        <v>28.6</v>
       </c>
       <c r="K57" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="58">
@@ -2865,22 +2887,22 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C58" t="n">
         <v>83.3</v>
       </c>
       <c r="D58" t="n">
-        <v>16.7</v>
+        <v>28.6</v>
       </c>
       <c r="E58" t="n">
-        <v>66.6</v>
+        <v>54.7</v>
       </c>
       <c r="F58" t="n">
-        <v>16.7</v>
+        <v>28.6</v>
       </c>
       <c r="G58" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>33.3</v>
@@ -2889,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2900,34 +2922,34 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C59" t="n">
-        <v>81.8</v>
+        <v>57.1</v>
       </c>
       <c r="D59" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="E59" t="n">
-        <v>72.7</v>
+        <v>32.1</v>
       </c>
       <c r="F59" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2935,31 +2957,31 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C60" t="n">
+        <v>100</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>66.7</v>
       </c>
-      <c r="D60" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="E60" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="F60" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="G60" t="n">
-        <v>9.1</v>
-      </c>
       <c r="H60" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>100</v>
@@ -2967,72 +2989,72 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E61" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C62" t="n">
-        <v>61.5</v>
+        <v>58.8</v>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>50.4</v>
+        <v>58.8</v>
       </c>
       <c r="F62" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>10</v>
       </c>
       <c r="H62" t="n">
-        <v>42.9</v>
+        <v>14.3</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="63">
@@ -3040,34 +3062,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="D63" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E63" t="n">
-        <v>63.5</v>
+        <v>66.6</v>
       </c>
       <c r="F63" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="G63" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I63" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3075,34 +3097,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
+        <v>67</v>
+      </c>
+      <c r="C64" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>20</v>
+      </c>
+      <c r="I64" t="n">
         <v>75</v>
       </c>
-      <c r="C64" t="n">
-        <v>88.9</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>88.9</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I64" t="n">
-        <v>80</v>
-      </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65">
@@ -3110,104 +3132,104 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C65" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E65" t="n">
-        <v>78.6</v>
+        <v>58.4</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G65" t="n">
         <v>9.1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I65" t="n">
-        <v>85.7</v>
+        <v>60</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" t="s">
         <v>80</v>
       </c>
-      <c r="B67" t="s">
-        <v>75</v>
-      </c>
       <c r="C67" t="n">
-        <v>80</v>
+        <v>61.5</v>
       </c>
       <c r="D67" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="F67" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="G67" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I67" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J67" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="K67" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3215,34 +3237,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C68" t="n">
         <v>85.7</v>
       </c>
       <c r="D68" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="E68" t="n">
-        <v>60.7</v>
+        <v>63.5</v>
       </c>
       <c r="F68" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="G68" t="n">
         <v>25</v>
       </c>
       <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>33.3</v>
       </c>
-      <c r="I68" t="n">
-        <v>50</v>
-      </c>
       <c r="J68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
@@ -3250,16 +3272,16 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C69" t="n">
-        <v>90.9</v>
+        <v>88.9</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>90.9</v>
+        <v>88.9</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3268,16 +3290,16 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -3285,34 +3307,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C70" t="n">
-        <v>77.8</v>
+        <v>78.6</v>
       </c>
       <c r="D70" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>61.1</v>
+        <v>78.6</v>
       </c>
       <c r="F70" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>4.2</v>
+        <v>9.1</v>
       </c>
       <c r="H70" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="J70" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3320,34 +3342,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C71" t="n">
-        <v>85.7</v>
+        <v>64.3</v>
       </c>
       <c r="D71" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>66.9</v>
+        <v>64.3</v>
       </c>
       <c r="F71" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="I71" t="n">
         <v>40</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72">
@@ -3355,66 +3377,66 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C72" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D72" t="n">
+        <v>25</v>
+      </c>
+      <c r="E72" t="n">
+        <v>55</v>
+      </c>
+      <c r="F72" t="n">
+        <v>25</v>
+      </c>
+      <c r="G72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J72" t="n">
         <v>14.3</v>
       </c>
-      <c r="E72" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F72" t="n">
+      <c r="K72" t="n">
         <v>14.3</v>
-      </c>
-      <c r="G72" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="H72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I72" t="n">
-        <v>50</v>
-      </c>
-      <c r="J72" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K72" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C73" t="n">
-        <v>55.6</v>
+        <v>85.7</v>
       </c>
       <c r="D73" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="E73" t="n">
-        <v>33.4</v>
+        <v>60.7</v>
       </c>
       <c r="F73" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="G73" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I73" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3422,142 +3444,142 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C74" t="n">
-        <v>80.8</v>
+        <v>90.9</v>
       </c>
       <c r="D74" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>62.6</v>
+        <v>90.9</v>
       </c>
       <c r="F74" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J74" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C75" t="n">
-        <v>91.7</v>
+        <v>77.8</v>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="E75" t="n">
-        <v>41.7</v>
+        <v>61.1</v>
       </c>
       <c r="F75" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="G75" t="n">
-        <v>21.4</v>
+        <v>4.2</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I75" t="n">
-        <v>28.6</v>
+        <v>66.7</v>
       </c>
       <c r="J75" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="K75" t="n">
-        <v>71.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C76" t="n">
-        <v>60</v>
+        <v>85.7</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="E76" t="n">
-        <v>60</v>
+        <v>66.9</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I76" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>90</v>
+      </c>
+      <c r="B77" t="s">
         <v>91</v>
       </c>
-      <c r="B77" t="s">
-        <v>86</v>
-      </c>
       <c r="C77" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D77" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="E77" t="n">
-        <v>80</v>
+        <v>52.4</v>
       </c>
       <c r="F77" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="G77" t="n">
-        <v>28.6</v>
+        <v>35.7</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I77" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="78">
@@ -3565,34 +3587,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C78" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="D78" t="n">
-        <v>8.3</v>
+        <v>22.2</v>
       </c>
       <c r="E78" t="n">
-        <v>66.7</v>
+        <v>33.4</v>
       </c>
       <c r="F78" t="n">
-        <v>8.3</v>
+        <v>22.2</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J78" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3600,34 +3622,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C79" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="E79" t="n">
-        <v>100</v>
+        <v>62.6</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="J79" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80">
@@ -3635,34 +3657,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C80" t="n">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="D80" t="n">
+        <v>50</v>
+      </c>
+      <c r="E80" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F80" t="n">
+        <v>50</v>
+      </c>
+      <c r="G80" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
         <v>28.6</v>
       </c>
-      <c r="E80" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="F80" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G80" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>33.3</v>
-      </c>
       <c r="J80" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="K80" t="n">
-        <v>16.7</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="81">
@@ -3670,34 +3692,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J81" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3705,34 +3727,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C82" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D82" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="E82" t="n">
-        <v>32.5</v>
+        <v>80</v>
       </c>
       <c r="F82" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="G82" t="n">
-        <v>17.6</v>
+        <v>28.6</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3740,101 +3762,101 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C83" t="n">
         <v>75</v>
       </c>
       <c r="D83" t="n">
-        <v>21.4</v>
+        <v>8.3</v>
       </c>
       <c r="E83" t="n">
-        <v>53.6</v>
+        <v>66.7</v>
       </c>
       <c r="F83" t="n">
-        <v>21.4</v>
+        <v>8.3</v>
       </c>
       <c r="G83" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K83" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C84" t="n">
-        <v>84.6</v>
+        <v>100</v>
       </c>
       <c r="D84" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>70.3</v>
+        <v>100</v>
       </c>
       <c r="F84" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>18.8</v>
+        <v>100</v>
       </c>
       <c r="K84" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C85" t="n">
-        <v>68.6</v>
+        <v>83.3</v>
       </c>
       <c r="D85" t="n">
-        <v>9.1</v>
+        <v>28.6</v>
       </c>
       <c r="E85" t="n">
-        <v>59.5</v>
+        <v>54.7</v>
       </c>
       <c r="F85" t="n">
-        <v>9.1</v>
+        <v>28.6</v>
       </c>
       <c r="G85" t="n">
-        <v>23.1</v>
+        <v>16.7</v>
       </c>
       <c r="H85" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>33.3</v>
       </c>
       <c r="J85" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="K85" t="n">
         <v>16.7</v>
@@ -3842,142 +3864,142 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C86" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I86" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C87" t="n">
-        <v>90.9</v>
+        <v>70</v>
       </c>
       <c r="D87" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="E87" t="n">
-        <v>70.9</v>
+        <v>32.5</v>
       </c>
       <c r="F87" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="G87" t="n">
-        <v>27.3</v>
+        <v>17.6</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J87" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K87" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D88" t="n">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
       <c r="E88" t="n">
-        <v>17.1</v>
+        <v>53.6</v>
       </c>
       <c r="F88" t="n">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
       <c r="G88" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="H88" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J88" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C89" t="n">
-        <v>90</v>
+        <v>84.6</v>
       </c>
       <c r="D89" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="E89" t="n">
-        <v>73.3</v>
+        <v>70.3</v>
       </c>
       <c r="F89" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="G89" t="n">
-        <v>18.2</v>
+        <v>13</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>33.3</v>
+        <v>43.8</v>
       </c>
       <c r="J89" t="n">
-        <v>50</v>
+        <v>18.8</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="90">
@@ -3985,34 +4007,34 @@
         <v>103</v>
       </c>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C90" t="n">
-        <v>100</v>
+        <v>68.6</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E90" t="n">
-        <v>100</v>
+        <v>59.5</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I90" t="n">
         <v>33.3</v>
       </c>
       <c r="J90" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="K90" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="91">
@@ -4020,93 +4042,101 @@
         <v>104</v>
       </c>
       <c r="B91" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
-      <c r="G91"/>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
-      <c r="I91"/>
-      <c r="J91"/>
-      <c r="K91"/>
+      <c r="I91" t="n">
+        <v>50</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>58.3</v>
+        <v>90.9</v>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E92" t="n">
-        <v>45.8</v>
+        <v>70.9</v>
       </c>
       <c r="F92" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G92" t="n">
-        <v>12.5</v>
+        <v>27.3</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C93" t="n">
+        <v>60</v>
+      </c>
+      <c r="D93" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E93" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G93" t="n">
         <v>33.3</v>
       </c>
-      <c r="D93" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F93" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G93" t="n">
-        <v>50</v>
-      </c>
       <c r="H93" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K93" t="n">
         <v>50</v>
@@ -4114,34 +4144,34 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C94" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D94" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E94" t="n">
-        <v>17.8</v>
+        <v>73.3</v>
       </c>
       <c r="F94" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="G94" t="n">
-        <v>75</v>
+        <v>18.2</v>
       </c>
       <c r="H94" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4149,171 +4179,165 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C95" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="D95" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="F95" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>33.3</v>
       </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>100</v>
-      </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>109</v>
+      </c>
+      <c r="B96" t="s">
         <v>110</v>
       </c>
-      <c r="B96" t="s">
-        <v>105</v>
-      </c>
       <c r="C96" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H96" t="n">
-        <v>20</v>
-      </c>
-      <c r="I96" t="n">
-        <v>50</v>
-      </c>
-      <c r="J96" t="n">
-        <v>50</v>
-      </c>
-      <c r="K96" t="n">
-        <v>50</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I96"/>
+      <c r="J96"/>
+      <c r="K96"/>
     </row>
     <row r="97">
       <c r="A97" t="s">
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C97" t="n">
-        <v>41.7</v>
+        <v>33.3</v>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
       <c r="F97" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
-      <c r="I97" t="n">
-        <v>100</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97"/>
+      <c r="J97"/>
+      <c r="K97"/>
     </row>
     <row r="98">
       <c r="A98" t="s">
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C98" t="n">
-        <v>16.7</v>
+        <v>61.1</v>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="E98" t="n">
-        <v>5.6</v>
+        <v>52</v>
       </c>
       <c r="F98" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="G98" t="n">
-        <v>50</v>
+        <v>8.3</v>
       </c>
       <c r="H98" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I98"/>
-      <c r="J98"/>
-      <c r="K98"/>
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>14.3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C99" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
       <c r="D99" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="E99" t="n">
-        <v>51.4</v>
+        <v>31.8</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="G99" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100">
@@ -4321,67 +4345,271 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C100" t="n">
+        <v>50</v>
+      </c>
+      <c r="D100" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F100" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G100" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I100" t="n">
         <v>66.7</v>
       </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
+      <c r="J100" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K100" t="n">
         <v>66.7</v>
       </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>115</v>
+      </c>
+      <c r="B101" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D101" t="n">
+        <v>25</v>
+      </c>
+      <c r="E101" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F101" t="n">
+        <v>25</v>
+      </c>
+      <c r="G101" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>100</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>116</v>
+      </c>
+      <c r="B102" t="s">
+        <v>110</v>
+      </c>
+      <c r="C102" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I102" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K102" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>31</v>
+      </c>
+      <c r="B103" t="s">
+        <v>110</v>
+      </c>
+      <c r="C103" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>100</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>117</v>
+      </c>
+      <c r="B104" t="s">
+        <v>110</v>
+      </c>
+      <c r="C104" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G104" t="n">
+        <v>50</v>
+      </c>
+      <c r="H104" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I104"/>
+      <c r="J104"/>
+      <c r="K104"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>118</v>
+      </c>
+      <c r="B105" t="s">
+        <v>110</v>
+      </c>
+      <c r="C105" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D105" t="n">
         <v>20</v>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
+      <c r="E105" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F105" t="n">
+        <v>20</v>
+      </c>
+      <c r="G105" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>50</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>119</v>
+      </c>
+      <c r="B106" t="s">
+        <v>110</v>
+      </c>
+      <c r="C106" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D106" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H106" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
         <v>100</v>
       </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101"/>
-      <c r="B101" t="s">
-        <v>115</v>
-      </c>
-      <c r="C101" t="n">
-        <v>67.6</v>
-      </c>
-      <c r="D101" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E101" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F101" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G101" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H101" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="I101" t="n">
-        <v>50</v>
-      </c>
-      <c r="J101" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="K101" t="n">
-        <v>29.6</v>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107"/>
+      <c r="B107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107" t="n">
+        <v>68</v>
+      </c>
+      <c r="D107" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F107" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H107" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I107" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>29.2</v>
       </c>
     </row>
   </sheetData>
@@ -4413,22 +4641,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -4437,13 +4665,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2">
@@ -4518,7 +4746,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -4553,7 +4781,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -4588,7 +4816,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -4623,7 +4851,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -4658,7 +4886,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -4728,7 +4956,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -4763,7 +4991,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -4798,7 +5026,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -4831,132 +5059,134 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="D13" t="n">
-        <v>63.3</v>
+        <v>65.4</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="F13" t="n">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="H13" t="n">
-        <v>53.3</v>
+        <v>46.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61.1</v>
+        <v>63.3</v>
       </c>
       <c r="E14" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>33.3</v>
       </c>
       <c r="G14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>53.3</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>43.6</v>
+        <v>61.1</v>
       </c>
       <c r="E15" t="n">
-        <v>8.8</v>
+        <v>12.5</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="G15" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
       <c r="H15" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="K15" t="n">
-        <v>-28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>33.3</v>
+        <v>53.3</v>
       </c>
       <c r="D16" t="n">
-        <v>36.8</v>
+        <v>43.6</v>
       </c>
       <c r="E16" t="n">
-        <v>7.7</v>
+        <v>8.8</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
-      </c>
-      <c r="H16"/>
+        <v>35.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>57.1</v>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -4964,214 +5194,212 @@
         <v>16.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-100</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>66.1</v>
+        <v>33.3</v>
       </c>
       <c r="D17" t="n">
-        <v>63.3</v>
+        <v>36.8</v>
       </c>
       <c r="E17" t="n">
-        <v>19.2</v>
+        <v>7.7</v>
       </c>
       <c r="F17" t="n">
-        <v>48.4</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>53.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H17"/>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K17" t="n">
-        <v>17.5</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>33.3</v>
+        <v>66.1</v>
       </c>
       <c r="D18" t="n">
-        <v>35.7</v>
+        <v>63.3</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>19.2</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="G18" t="n">
-        <v>16.7</v>
+        <v>7.1</v>
       </c>
       <c r="H18" t="n">
-        <v>33.3</v>
+        <v>53.7</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.7</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>70</v>
+        <v>33.3</v>
       </c>
       <c r="D19" t="n">
-        <v>48.6</v>
+        <v>35.7</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>20</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>23.1</v>
-      </c>
       <c r="K19" t="n">
-        <v>-10</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C20" t="n">
-        <v>76.8</v>
+        <v>70</v>
       </c>
       <c r="D20" t="n">
-        <v>66.7</v>
+        <v>48.6</v>
       </c>
       <c r="E20" t="n">
-        <v>13.6</v>
+        <v>5.3</v>
       </c>
       <c r="F20" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>47.7</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>15.7</v>
+        <v>23.1</v>
       </c>
       <c r="K20" t="n">
-        <v>8.9</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>76.8</v>
       </c>
       <c r="D21" t="n">
-        <v>57.5</v>
+        <v>66.7</v>
       </c>
       <c r="E21" t="n">
-        <v>5.1</v>
+        <v>13.6</v>
       </c>
       <c r="F21" t="n">
-        <v>27.3</v>
+        <v>44.4</v>
       </c>
       <c r="G21" t="n">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="H21" t="n">
-        <v>54.5</v>
+        <v>47.7</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>21.1</v>
+        <v>15.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C22" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>57.5</v>
       </c>
       <c r="E22" t="n">
-        <v>18.2</v>
+        <v>5.1</v>
       </c>
       <c r="F22" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="G22" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="H22" t="n">
-        <v>25</v>
+        <v>54.5</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -5179,156 +5407,156 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C23" t="n">
-        <v>37.5</v>
+        <v>83.3</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>4.5</v>
+        <v>18.2</v>
       </c>
       <c r="F23" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H23" t="n">
         <v>25</v>
       </c>
-      <c r="G23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>38.5</v>
-      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C24" t="n">
-        <v>51.4</v>
+        <v>37.5</v>
       </c>
       <c r="D24" t="n">
-        <v>59.4</v>
+        <v>54</v>
       </c>
       <c r="E24" t="n">
-        <v>13.2</v>
+        <v>4.5</v>
       </c>
       <c r="F24" t="n">
-        <v>42.1</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="H24" t="n">
-        <v>45.5</v>
+        <v>38.5</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>27</v>
+        <v>18.2</v>
       </c>
       <c r="K24" t="n">
-        <v>11.5</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C25" t="n">
-        <v>80</v>
+        <v>51.4</v>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>59.4</v>
       </c>
       <c r="E25" t="n">
-        <v>28.6</v>
+        <v>13.2</v>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>42.1</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>11.4</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>45.5</v>
+        <v>27</v>
       </c>
       <c r="K25" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D26" t="n">
-        <v>57.1</v>
+        <v>64</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="K26" t="n">
         <v>40</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-16.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C27" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5337,283 +5565,283 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H27" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>57.9</v>
+        <v>33.3</v>
       </c>
       <c r="D28" t="n">
         <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>-11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C29" t="n">
-        <v>62.8</v>
+        <v>57.9</v>
       </c>
       <c r="D29" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>9.3</v>
       </c>
       <c r="F29" t="n">
-        <v>41.7</v>
+        <v>12.5</v>
       </c>
       <c r="G29" t="n">
-        <v>9.3</v>
+        <v>16.7</v>
       </c>
       <c r="H29" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.3</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30"/>
+        <v>7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>41.7</v>
+      </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H30" t="n">
-        <v>33.3</v>
+        <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C31" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F31"/>
       <c r="G31" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I31" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C32" t="n">
-        <v>71.4</v>
+        <v>28.6</v>
       </c>
       <c r="D32" t="n">
-        <v>70.2</v>
+        <v>37.5</v>
       </c>
       <c r="E32" t="n">
-        <v>23.5</v>
+        <v>9.5</v>
       </c>
       <c r="F32" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J32" t="n">
-        <v>34.8</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>28.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C33" t="n">
-        <v>66.7</v>
+        <v>71.4</v>
       </c>
       <c r="D33" t="n">
-        <v>66.7</v>
+        <v>70.2</v>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>23.5</v>
       </c>
       <c r="F33" t="n">
         <v>50</v>
       </c>
       <c r="G33" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>18.2</v>
+        <v>40</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>19.2</v>
+        <v>34.8</v>
       </c>
       <c r="K33" t="n">
-        <v>6.6</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34"/>
+        <v>30</v>
+      </c>
+      <c r="F34" t="n">
+        <v>50</v>
+      </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C35" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D35" t="n">
-        <v>57.8</v>
+        <v>80</v>
       </c>
       <c r="E35" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F35" t="n">
-        <v>41.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35"/>
       <c r="G35" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>50</v>
@@ -5622,269 +5850,269 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C36" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D36" t="n">
-        <v>87.5</v>
+        <v>57.8</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="H36" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C37" t="n">
-        <v>69.2</v>
+        <v>100</v>
       </c>
       <c r="D37" t="n">
-        <v>74.7</v>
+        <v>87.5</v>
       </c>
       <c r="E37" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C38" t="n">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="D38" t="n">
-        <v>63.2</v>
+        <v>74.7</v>
       </c>
       <c r="E38" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="F38" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="H38" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>21.4</v>
+        <v>24.4</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C39" t="n">
-        <v>58.3</v>
+        <v>61.5</v>
       </c>
       <c r="D39" t="n">
-        <v>65.3</v>
+        <v>63.2</v>
       </c>
       <c r="E39" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="F39" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H39" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>12.5</v>
+        <v>21.4</v>
       </c>
       <c r="K39" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C40" t="n">
-        <v>40</v>
+        <v>58.3</v>
       </c>
       <c r="D40" t="n">
-        <v>41.2</v>
+        <v>65.3</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K40" t="n">
-        <v>-20</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>14.3</v>
+        <v>40</v>
       </c>
       <c r="D41" t="n">
-        <v>44.1</v>
+        <v>41.2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
         <v>33.3</v>
       </c>
-      <c r="G41" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>50</v>
-      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>-14.3</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D42" t="n">
-        <v>38.9</v>
+        <v>44.1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G42" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K42" t="n">
-        <v>-66.7</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>57.9</v>
+        <v>38.9</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -5893,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5902,447 +6130,620 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>-25</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C44" t="n">
         <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>41.4</v>
+        <v>57.9</v>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="K44" t="n">
-        <v>-16.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
+        <v>41.4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>15</v>
+      </c>
+      <c r="F45" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>50</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-16.6</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C46" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="E46" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F46" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="G46" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>25</v>
-      </c>
-      <c r="K46" t="n">
-        <v>8.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D47" t="n">
-        <v>59.3</v>
+        <v>57.5</v>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>51.9</v>
       </c>
       <c r="G47" t="n">
-        <v>7.1</v>
+        <v>20.8</v>
       </c>
       <c r="H47" t="n">
-        <v>40</v>
+        <v>47.8</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C48" t="n">
         <v>50</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="E48" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="G48" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H48" t="n">
         <v>40</v>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>29.4</v>
+        <v>8.3</v>
       </c>
       <c r="K48" t="n">
-        <v>16.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C49" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H49" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
-        <v>33.3</v>
+        <v>29.4</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>87.5</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50"/>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
       <c r="G50" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C51" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>63.4</v>
+        <v>20</v>
       </c>
       <c r="E51" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F51" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F51"/>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H51" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>27.8</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C52" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D52" t="n">
-        <v>80</v>
+        <v>63.4</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C53" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D53" t="n">
-        <v>31.6</v>
+        <v>80</v>
       </c>
       <c r="E53" t="n">
-        <v>7.1</v>
+        <v>50</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C54" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D54" t="n">
-        <v>53.3</v>
+        <v>31.6</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="H54" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>7.1</v>
+        <v>33.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-11.1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C55" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D55" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55"/>
+      <c r="G55" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" t="n">
+        <v>50</v>
+      </c>
+      <c r="D56" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>175</v>
+      </c>
+      <c r="B57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" t="n">
+        <v>100</v>
+      </c>
+      <c r="D58" t="n">
+        <v>60</v>
+      </c>
+      <c r="E58" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>100</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>50</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" t="n">
         <v>52</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D59" t="n">
         <v>55.2</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E59" t="n">
         <v>9.1</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F59" t="n">
         <v>28.6</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G59" t="n">
         <v>8</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H59" t="n">
         <v>47.4</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J59" t="n">
         <v>14.3</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56"/>
-      <c r="B56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="E56" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F56" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="G56" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H56" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K56" t="n">
-        <v>-3.8</v>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" t="n">
+        <v>70.6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16</v>
+      </c>
+      <c r="F60" t="n">
+        <v>50</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>50</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J60" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61"/>
+      <c r="B61" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" t="n">
+        <v>57</v>
+      </c>
+      <c r="D61" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>12</v>
+      </c>
+      <c r="F61" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H61" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-3.9</v>
       </c>
     </row>
   </sheetData>
